--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$133</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$135</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (119 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 132 řádků.</t>
+          <t>HSV položkově (121 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 134 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 33 sklad = 234 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 37 sklad = 238 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>234 (201 dum + 33 sklad)</t>
+          <t>238 (201 dum + 37 sklad)</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 119 | M 2 | PSV 56 | TZB 34 | VRN 23</t>
+          <t>HSV 121 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 35 | 0.90: 32 | 0.85: 41 | 0.80: 21 | 0.75: 70 | 0.70: 4 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 32 | 0.90: 32 | 0.85: 45 | 0.80: 21 | 0.75: 70 | 0.70: 7 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 157 needs_production_lookup (67.1 %)</t>
+          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 161 needs_production_lookup (67.6 %)</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>31 items (viz Otazky_pro_Karla docx)</t>
+          <t>34 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1186,8 +1186,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-234 položek celkem (201 dum + 33 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 35×0.95 · 32×0.90 · 41×0.85 · 21×0.80 · 70×0.75 · 4×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+238 položek celkem (201 dum + 37 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 32×0.95 · 32×0.90 · 45×0.85 · 21×0.80 · 70×0.75 · 7×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -2962,11 +2962,11 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Sejmutí stávající zídky + schodiště; Hloubení figury skladu; Hloubení rýh pro pasy; Hloubení parkingových patek; … (+2 dalších)</t>
+          <t>Sejmutí stávající zídky + schodiště; Hloubení figury skladu; Hloubení rýh pro pasy; Hloubení parkingových patek; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E2" s="10" t="n"/>
       <c r="F2" s="10" t="n"/>
@@ -3087,11 +3087,11 @@
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); Zábradlí stání</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E7" s="10" t="n"/>
       <c r="F7" s="10" t="n"/>
@@ -3163,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J133"/>
+  <dimension ref="A1:J135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3735,7 +3735,7 @@
         </is>
       </c>
       <c r="F14" s="22" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu — Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + zalití C25/30</t>
+          <t>Tvarovky ZB obvod skladu — Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="E43" s="20" t="inlineStr">
@@ -4895,7 +4895,7 @@
         </is>
       </c>
       <c r="F43" s="22" t="n">
-        <v>46.5</v>
+        <v>62.5</v>
       </c>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n"/>
@@ -4935,7 +4935,7 @@
         </is>
       </c>
       <c r="F44" s="22" t="n">
-        <v>1398</v>
+        <v>1875</v>
       </c>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="10" t="n"/>
@@ -7989,34 +7989,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C121" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C121" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 2 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána</t>
+          <t>Kladecí lože pod dlažbu — Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skladu</t>
         </is>
       </c>
       <c r="E121" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F121" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F121" s="22" t="n">
+        <v>0.9399999999999999</v>
       </c>
       <c r="G121" s="10" t="n"/>
       <c r="H121" s="10" t="n"/>
       <c r="I121" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J121" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 564231111</t>
         </is>
       </c>
     </row>
@@ -8029,34 +8029,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C122" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C122" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Zásyp za prefa opěrnou stěnou — Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuveden v legendě, OVĚŘIT)</t>
         </is>
       </c>
       <c r="E122" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F122" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F122" s="22" t="n">
+        <v>23.5</v>
       </c>
       <c r="G122" s="10" t="n"/>
       <c r="H122" s="10" t="n"/>
       <c r="I122" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="J122" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 174101101</t>
         </is>
       </c>
     </row>
@@ -8071,12 +8071,12 @@
       </c>
       <c r="C123" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
@@ -8106,17 +8106,17 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C124" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
@@ -8146,17 +8146,17 @@
       </c>
       <c r="B125" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C125" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="C126" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
@@ -8231,12 +8231,12 @@
       </c>
       <c r="C127" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="C128" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="C129" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="C130" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="C131" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="C132" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
@@ -8471,12 +8471,12 @@
       </c>
       <c r="C133" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
@@ -8500,8 +8500,88 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="20" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C134" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D134" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E134" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F134" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" s="10" t="n"/>
+      <c r="H134" s="10" t="n"/>
+      <c r="I134" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J134" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="20" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C135" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D135" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E135" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F135" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" s="10" t="n"/>
+      <c r="H135" s="10" t="n"/>
+      <c r="I135" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J135" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J133"/>
+  <autoFilter ref="A1:J135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22343,7 +22423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R34"/>
+  <dimension ref="A1:R38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -22756,7 +22836,7 @@
         </is>
       </c>
       <c r="G6" s="22" t="n">
-        <v>2.64</v>
+        <v>3.54</v>
       </c>
       <c r="H6" s="10" t="n"/>
       <c r="I6" s="10" t="n"/>
@@ -22766,7 +22846,7 @@
         </is>
       </c>
       <c r="K6" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L6" s="20" t="inlineStr">
         <is>
@@ -22775,7 +22855,7 @@
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t>DXF podlaha skladu 6.35×3.34 = 21.2 m²</t>
+          <t>legenda místností 17.6 m² + vynos S01 za stěnu 6010×1000 mm dle řezu B-B (neviditelný na půdorysu)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -22795,7 +22875,7 @@
       </c>
       <c r="Q6" s="41" t="inlineStr">
         <is>
-          <t>W1_PODLAHA_17.6_2026-06-01</t>
+          <t>S01_AREA_23.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -22873,22 +22953,22 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>HSV-2 Základové a ŽB</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy sklad</t>
-        </is>
-      </c>
-      <c r="D8" s="27" t="inlineStr">
-        <is>
-          <t>271313??? ?</t>
+          <t>Kladecí lože pod dlažbu</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>564231111</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
+          <t>Kladecí lože z kamenné drti 4-8 mm tl. 40 mm pod betonovou dlažbu skladu</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -22897,26 +22977,26 @@
         </is>
       </c>
       <c r="G8" s="22" t="n">
-        <v>4.84</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H8" s="10" t="n"/>
       <c r="I8" s="10" t="n"/>
       <c r="J8" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K8" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L8" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M8" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ + TZ statika sklad §4 — C16/20 XC0 pasy 500×500</t>
+          <t>skladba S01 — kladecí vrstva kamenná drť 4-8 mm 40 mm (vrstva dříve chyběla)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -22924,14 +23004,14 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
+      <c r="O8" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
         </is>
       </c>
       <c r="P8" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S01_sklad</t>
         </is>
       </c>
       <c r="Q8" s="41" t="n"/>
@@ -22942,55 +23022,55 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>HSV-2 Základové a ŽB</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — spodní</t>
+          <t>Zásyp za prefa opěrnou stěnou</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
         <is>
-          <t>273313811</t>
+          <t>174101101</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
+          <t>Zásyp za prefabrikovanou opěrnou stěnou S04 — materiál dle PD (NEuveden v legendě, OVĚŘIT)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>6</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>23.5</v>
       </c>
       <c r="H9" s="10" t="n"/>
       <c r="I9" s="10" t="n"/>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.95</v>
+        <v>0.7</v>
       </c>
       <c r="L9" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M9" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
+          <t>řez A-A — klín zásypu za S04; materiál v legendě NEuveden → OVĚŘIT</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>#36</t>
         </is>
       </c>
       <c r="O9" s="26" t="inlineStr">
@@ -22998,12 +23078,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P9" s="41" t="n"/>
-      <c r="Q9" s="41" t="inlineStr">
-        <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P9" s="41" t="inlineStr"/>
+      <c r="Q9" s="41" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="20" t="n">
@@ -23016,26 +23092,26 @@
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — horní</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>311233812</t>
+          <t>Základové pasy sklad</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>271313??? ?</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>6</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>4.84</v>
       </c>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
@@ -23049,12 +23125,12 @@
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
+          <t>DXF sklad_DPZ + TZ statika sklad §4 — C16/20 XC0 pasy 500×500</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -23062,17 +23138,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O10" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P10" s="41" t="n"/>
-      <c r="Q10" s="41" t="inlineStr">
-        <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="O10" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P10" s="41" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S03b_sklad</t>
+        </is>
+      </c>
+      <c r="Q10" s="41" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="20" t="n">
@@ -23085,26 +23161,26 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Beton patek + zídek — zalití</t>
+          <t>Patky parking — spodní</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>273321321</t>
+          <t>273313811</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
+          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>1.75</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>6</v>
       </c>
       <c r="H11" s="10" t="n"/>
       <c r="I11" s="10" t="n"/>
@@ -23114,21 +23190,21 @@
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 (6 patek)</t>
+          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O11" s="26" t="inlineStr">
@@ -23154,32 +23230,32 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože</t>
+          <t>Patky parking — horní</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
         <is>
-          <t>174101101</t>
+          <t>311233812</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>1.76</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>6</v>
       </c>
       <c r="H12" s="10" t="n"/>
       <c r="I12" s="10" t="n"/>
       <c r="J12" s="8" t="inlineStr">
         <is>
-          <t>zemni_prace</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K12" s="24" t="n">
@@ -23187,12 +23263,12 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_cross_discipline_legitimate</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>DXF + TZ statika sklad</t>
+          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -23205,14 +23281,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P12" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad, S05_sklad</t>
-        </is>
-      </c>
+      <c r="P12" s="41" t="n"/>
       <c r="Q12" s="41" t="inlineStr">
         <is>
-          <t>W1_PODLAHA_17.6_2026-06-01</t>
+          <t>PATKY_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23227,17 +23299,17 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Schodišťová deska + pas</t>
+          <t>Beton patek + zídek — zalití</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273321321</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -23246,7 +23318,7 @@
         </is>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n"/>
@@ -23265,7 +23337,7 @@
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — prefa schodové dílce + ŽB pas</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 (6 patek)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -23278,12 +23350,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P13" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
-      <c r="Q13" s="41" t="n"/>
+      <c r="P13" s="41" t="n"/>
+      <c r="Q13" s="41" t="inlineStr">
+        <is>
+          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
@@ -23291,50 +23363,50 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna</t>
+          <t>Štěrkopískové lože</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>311233815</t>
+          <t>174101101</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G14" s="23" t="n">
-        <v>18</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>1.76</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_cross_discipline_legitimate</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+          <t>DXF + TZ statika sklad</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23349,12 +23421,12 @@
       </c>
       <c r="P14" s="41" t="inlineStr">
         <is>
-          <t>S04_sklad</t>
+          <t>S01_sklad, S05_sklad</t>
         </is>
       </c>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
+          <t>W1_PODLAHA_17.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23364,41 +23436,41 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu</t>
+          <t>Schodišťová deska + pas</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>311233811</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu — tvarovky ztraceného bednění tl. 250 mm × výška 2.4 m + zalití C25/30</t>
+          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>46.5</v>
+        <v>0.8</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -23407,7 +23479,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION obvod</t>
+          <t>TZ statika sklad §4 — prefa schodové dílce + ŽB pas</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23422,7 +23494,7 @@
       </c>
       <c r="P15" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S05_sklad</t>
         </is>
       </c>
       <c r="Q15" s="41" t="n"/>
@@ -23438,50 +23510,50 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>1398</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>18</v>
       </c>
       <c r="H16" s="10" t="n"/>
       <c r="I16" s="10" t="n"/>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>B4_productivity Methvin — výztuž do ZB tvarovek tl. 250 mm</t>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O16" s="26" t="inlineStr">
@@ -23491,12 +23563,12 @@
       </c>
       <c r="P16" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S04_sklad</t>
         </is>
       </c>
       <c r="Q16" s="41" t="inlineStr">
         <is>
-          <t>URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23511,17 +23583,17 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
+          <t>Tvarovky ZB obvod skladu</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311233811</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -23530,17 +23602,17 @@
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -23549,7 +23621,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -23564,12 +23636,12 @@
       </c>
       <c r="P17" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q17" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23584,50 +23656,49 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
+          <t>Výztuž ZB tvarovek</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G18" s="22" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04</t>
-        </is>
+          <t>family_verified_leaf_needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M18" s="8">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="O18" s="26" t="inlineStr">
@@ -23637,12 +23708,12 @@
       </c>
       <c r="P18" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q18" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23652,41 +23723,41 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>36.74</v>
+        <v>33</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
@@ -23695,7 +23766,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -23710,12 +23781,12 @@
       </c>
       <c r="P19" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q19" s="41" t="inlineStr">
         <is>
-          <t>DS3_STROPNICE_11_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23725,22 +23796,22 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -23749,17 +23820,17 @@
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>21.209</v>
+        <v>33</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
@@ -23768,7 +23839,7 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -23783,10 +23854,14 @@
       </c>
       <c r="P20" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="Q20" s="41" t="n"/>
+          <t>S03a_sklad, S04_sklad</t>
+        </is>
+      </c>
+      <c r="Q20" s="41" t="inlineStr">
+        <is>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="20" t="n">
@@ -23799,32 +23874,32 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>22.26945</v>
+        <v>36.74</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
@@ -23837,7 +23912,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — HI souvrství</t>
+          <t>TZ statika sklad §4 + DXF DIMENSION</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -23855,7 +23930,11 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q21" s="41" t="n"/>
+      <c r="Q21" s="41" t="inlineStr">
+        <is>
+          <t>DS3_STROPNICE_11_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="20" t="n">
@@ -23868,36 +23947,36 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>790</v>
+        <v>21.209</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
@@ -23906,12 +23985,12 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+          <t>TZ statika sklad §4 + DXF</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O22" s="26" t="inlineStr">
@@ -23924,11 +24003,7 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q22" s="41" t="inlineStr">
-        <is>
-          <t>IPE_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="Q22" s="41" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n">
@@ -23941,17 +24016,17 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -23960,26 +24035,26 @@
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>44.6</v>
+        <v>22.26945</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §4 — HI souvrství</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -23997,11 +24072,7 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q23" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
-        </is>
-      </c>
+      <c r="Q23" s="41" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="20" t="n">
@@ -24014,17 +24085,17 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -24033,7 +24104,7 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
@@ -24043,20 +24114,21 @@
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M24" s="8">
-        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
-        <v/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+        </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O24" s="26" t="inlineStr">
@@ -24081,22 +24153,22 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -24105,26 +24177,26 @@
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M25" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -24139,12 +24211,12 @@
       </c>
       <c r="P25" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q25" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -24154,49 +24226,50 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G26" s="22" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="n">
+        <v>1420</v>
+      </c>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
-        </is>
+      <c r="M26" s="8">
+        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
+        <v/>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
@@ -24208,10 +24281,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P26" s="41" t="inlineStr"/>
+      <c r="P26" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
       <c r="Q26" s="41" t="inlineStr">
         <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+          <t>IPE_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24221,41 +24298,41 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Sklad mezipodesta schodiště prefa</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G27" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
@@ -24264,7 +24341,7 @@
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24277,8 +24354,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P27" s="41" t="n"/>
-      <c r="Q27" s="41" t="n"/>
+      <c r="P27" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q27" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="20" t="n">
@@ -24286,12 +24371,12 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -24301,26 +24386,24 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G28" s="23" t="n">
-        <v>1</v>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="n"/>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
@@ -24329,7 +24412,7 @@
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
         </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
@@ -24355,50 +24438,50 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D29" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
+        </is>
+      </c>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G29" s="22" t="n">
-        <v>17.6</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G29" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24406,21 +24489,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O29" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P29" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q29" s="41" t="inlineStr">
-        <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY</t>
-        </is>
-      </c>
+      <c r="O29" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P29" s="41" t="n"/>
+      <c r="Q29" s="41" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="20" t="n">
@@ -24428,41 +24503,41 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Oplocení (plot)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G30" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G30" s="22" t="n">
+        <v>3.8</v>
       </c>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
@@ -24471,12 +24546,12 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#37</t>
         </is>
       </c>
       <c r="O30" s="26" t="inlineStr">
@@ -24484,7 +24559,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P30" s="41" t="n"/>
+      <c r="P30" s="41" t="inlineStr"/>
       <c r="Q30" s="41" t="n"/>
     </row>
     <row r="31">
@@ -24493,41 +24568,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
+          <t>Zábradlí stání</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>8</v>
+        <v>18.5</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -24536,12 +24611,12 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#38</t>
         </is>
       </c>
       <c r="O31" s="26" t="inlineStr">
@@ -24549,7 +24624,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P31" s="41" t="n"/>
+      <c r="P31" s="41" t="inlineStr"/>
       <c r="Q31" s="41" t="n"/>
     </row>
     <row r="32">
@@ -24558,27 +24633,27 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G32" s="23" t="n">
@@ -24588,11 +24663,11 @@
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
-        <v>0.99</v>
+        <v>0.6</v>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
@@ -24601,7 +24676,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -24614,8 +24689,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P32" s="41" t="n"/>
-      <c r="Q32" s="41" t="n"/>
+      <c r="P32" s="41" t="inlineStr"/>
+      <c r="Q32" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n">
@@ -24623,50 +24702,50 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
-        </is>
-      </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>—</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D33" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G33" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G33" s="22" t="n">
+        <v>23.6</v>
       </c>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K33" s="24" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="L33" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -24674,15 +24753,19 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O33" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P33" s="41" t="inlineStr"/>
+      <c r="O33" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P33" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
       <c r="Q33" s="41" t="inlineStr">
         <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+          <t>S01_AREA_23.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24692,27 +24775,27 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G34" s="23" t="n">
@@ -24722,11 +24805,11 @@
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K34" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L34" s="20" t="inlineStr">
         <is>
@@ -24735,7 +24818,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -24751,9 +24834,273 @@
       <c r="P34" s="41" t="n"/>
       <c r="Q34" s="41" t="n"/>
     </row>
+    <row r="35">
+      <c r="A35" s="20" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace odpadu sklad</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>997013211</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G35" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H35" s="10" t="n"/>
+      <c r="I35" s="10" t="n"/>
+      <c r="J35" s="8" t="inlineStr">
+        <is>
+          <t>bourani_demolice</t>
+        </is>
+      </c>
+      <c r="K35" s="24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M35" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+        </is>
+      </c>
+      <c r="N35" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O35" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P35" s="41" t="n"/>
+      <c r="Q35" s="41" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>030141000</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+        </is>
+      </c>
+      <c r="F36" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G36" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="10" t="n"/>
+      <c r="I36" s="10" t="n"/>
+      <c r="J36" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K36" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+        </is>
+      </c>
+      <c r="N36" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O36" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P36" s="41" t="n"/>
+      <c r="Q36" s="41" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F37" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G37" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="10" t="n"/>
+      <c r="I37" s="10" t="n"/>
+      <c r="J37" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M37" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N37" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O37" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P37" s="41" t="inlineStr"/>
+      <c r="Q37" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="20" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F38" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G38" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="10" t="n"/>
+      <c r="I38" s="10" t="n"/>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L38" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N38" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O38" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P38" s="41" t="n"/>
+      <c r="Q38" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O34"/>
-  <conditionalFormatting sqref="K2:K34">
+  <autoFilter ref="A1:O38"/>
+  <conditionalFormatting sqref="K2:K38">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
@@ -26957,7 +27304,7 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba do pískového lože — povrch podlahy skladu (~21 m²)…</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu…</t>
         </is>
       </c>
       <c r="G7" s="8" t="inlineStr">

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (121 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 134 řádků.</t>
+          <t>HSV položkově (130 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 143 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 37 sklad = 238 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 46 sklad = 247 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>238 (201 dum + 37 sklad)</t>
+          <t>247 (201 dum + 46 sklad)</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 121 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
+          <t>HSV 130 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 32 | 0.90: 32 | 0.85: 45 | 0.80: 21 | 0.75: 70 | 0.70: 7 | 0.60: 3 | 0.50: 6 | 0.00: 5</t>
+          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 9 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.4 %) ✓ | 5 wrong leaf flagged (2.1 %) ⚠ | 161 needs_production_lookup (67.6 %)</t>
+          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 170 needs_production_lookup (68.8 %)</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>34 items (viz Otazky_pro_Karla docx)</t>
+          <t>37 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1186,8 +1186,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-238 položek celkem (201 dum + 37 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 32×0.95 · 32×0.90 · 45×0.85 · 21×0.80 · 70×0.75 · 7×0.70 · 3×0.60 · 6×0.50 · 5×0.00.
+247 položek celkem (201 dum + 46 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 9×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -2962,11 +2962,11 @@
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>Sejmutí stávající zídky + schodiště; Hloubení figury skladu; Hloubení rýh pro pasy; Hloubení parkingových patek; … (+4 dalších)</t>
+          <t>Sejmutí stávající zídky + schodiště; Hloubení figury skladu; Hloubení rýh pro pasy; Hloubení parkingových patek; … (+6 dalších)</t>
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="10" t="n"/>
       <c r="F2" s="10" t="n"/>
@@ -3062,11 +3062,11 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa; Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Schodiště prefa stupně; Vjezd Dvořákova — napojení na komunikaci; Vjezd — pískové lože; Vjezd — štěrkový podklad; … (+5 dalších)</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E6" s="10" t="n"/>
       <c r="F6" s="10" t="n"/>
@@ -3163,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J135"/>
+  <dimension ref="A1:J144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5535,7 +5535,7 @@
         </is>
       </c>
       <c r="F59" s="22" t="n">
-        <v>36.74</v>
+        <v>31</v>
       </c>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n"/>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="F60" s="22" t="n">
-        <v>21.209</v>
+        <v>18.1</v>
       </c>
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n"/>
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="F61" s="22" t="n">
-        <v>22.26945</v>
+        <v>19</v>
       </c>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa — Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Schodiště prefa stupně — Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="E103" s="20" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci — Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci — Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
         </is>
       </c>
       <c r="E118" s="20" t="inlineStr">
@@ -7886,7 +7886,9 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="F118" s="22" t="n"/>
+      <c r="F118" s="22" t="n">
+        <v>7</v>
+      </c>
       <c r="G118" s="10" t="n"/>
       <c r="H118" s="10" t="n"/>
       <c r="I118" s="8" t="inlineStr">
@@ -8069,34 +8071,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C123" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C123" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
+          <t>Vjezd — pískové lože — Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
         </is>
       </c>
       <c r="E123" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F123" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F123" s="22" t="n">
+        <v>0.28</v>
       </c>
       <c r="G123" s="10" t="n"/>
       <c r="H123" s="10" t="n"/>
       <c r="I123" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J123" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 564751111</t>
         </is>
       </c>
     </row>
@@ -8109,34 +8111,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C124" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C124" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Vjezd — štěrkový podklad — Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
         </is>
       </c>
       <c r="E124" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F124" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F124" s="22" t="n">
+        <v>1.05</v>
       </c>
       <c r="G124" s="10" t="n"/>
       <c r="H124" s="10" t="n"/>
       <c r="I124" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J124" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 564861111</t>
         </is>
       </c>
     </row>
@@ -8149,34 +8151,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C125" s="21" t="inlineStr">
-        <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+      <c r="C125" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>Odvodňovací žlab — Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
         </is>
       </c>
       <c r="E125" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F125" s="9" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="F125" s="22" t="n">
+        <v>7.775</v>
       </c>
       <c r="G125" s="10" t="n"/>
       <c r="H125" s="10" t="n"/>
       <c r="I125" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J125" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8186,37 +8188,37 @@
       </c>
       <c r="B126" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C126" s="21" t="inlineStr">
-        <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C126" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>Odvodňovací žlab — podkladní beton — Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="E126" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F126" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F126" s="22" t="n">
+        <v>0.47</v>
       </c>
       <c r="G126" s="10" t="n"/>
       <c r="H126" s="10" t="n"/>
       <c r="I126" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J126" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273321411</t>
         </is>
       </c>
     </row>
@@ -8226,37 +8228,37 @@
       </c>
       <c r="B127" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C127" s="21" t="inlineStr">
-        <is>
-          <t>M-24</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C127" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>Okapový žlab — Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
         </is>
       </c>
       <c r="E127" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F127" s="9" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="F127" s="22" t="n">
+        <v>6</v>
       </c>
       <c r="G127" s="10" t="n"/>
       <c r="H127" s="10" t="n"/>
       <c r="I127" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J127" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8266,37 +8268,37 @@
       </c>
       <c r="B128" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C128" s="21" t="inlineStr">
-        <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C128" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>Trubka u pasu — vysoký pas — Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvětrání radonu (OVĚŘIT)</t>
         </is>
       </c>
       <c r="E128" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F128" s="9" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="F128" s="22" t="n">
+        <v>6.35</v>
       </c>
       <c r="G128" s="10" t="n"/>
       <c r="H128" s="10" t="n"/>
       <c r="I128" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="J128" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8306,37 +8308,37 @@
       </c>
       <c r="B129" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C129" s="21" t="inlineStr">
-        <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C129" s="8" t="inlineStr">
+        <is>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>Trubka u pasu — podél stěny — Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání radonu (OVĚŘIT)</t>
         </is>
       </c>
       <c r="E129" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F129" s="9" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="F129" s="22" t="n">
+        <v>6.01</v>
       </c>
       <c r="G129" s="10" t="n"/>
       <c r="H129" s="10" t="n"/>
       <c r="I129" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="J129" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8346,37 +8348,37 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C130" s="21" t="inlineStr">
-        <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C130" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>Schodiště — podkladní deska — Podkladní betonová deska pod prefa schodiště S05</t>
         </is>
       </c>
       <c r="E130" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F130" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F130" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="G130" s="10" t="n"/>
       <c r="H130" s="10" t="n"/>
       <c r="I130" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="J130" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273313611</t>
         </is>
       </c>
     </row>
@@ -8386,37 +8388,37 @@
       </c>
       <c r="B131" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
-        </is>
-      </c>
-      <c r="C131" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>260217_sklad</t>
+        </is>
+      </c>
+      <c r="C131" s="8" t="inlineStr">
+        <is>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>Schodiště — kladecí beton — Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
         </is>
       </c>
       <c r="E131" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F131" s="9" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="F131" s="22" t="n">
+        <v>0.28</v>
       </c>
       <c r="G131" s="10" t="n"/>
       <c r="H131" s="10" t="n"/>
       <c r="I131" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="J131" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop —</t>
         </is>
       </c>
     </row>
@@ -8426,17 +8428,17 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C132" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
@@ -8466,17 +8468,17 @@
       </c>
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C133" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
@@ -8506,17 +8508,17 @@
       </c>
       <c r="B134" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C134" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
@@ -8551,12 +8553,12 @@
       </c>
       <c r="C135" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E135" s="20" t="inlineStr">
@@ -8580,8 +8582,368 @@
         </is>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" s="20" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C136" s="21" t="inlineStr">
+        <is>
+          <t>M-24</t>
+        </is>
+      </c>
+      <c r="D136" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+        </is>
+      </c>
+      <c r="E136" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F136" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" s="10" t="n"/>
+      <c r="H136" s="10" t="n"/>
+      <c r="I136" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J136" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="20" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C137" s="21" t="inlineStr">
+        <is>
+          <t>PSV-71 — Izolace HI + TI</t>
+        </is>
+      </c>
+      <c r="D137" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+        </is>
+      </c>
+      <c r="E137" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F137" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G137" s="10" t="n"/>
+      <c r="H137" s="10" t="n"/>
+      <c r="I137" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J137" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="20" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C138" s="21" t="inlineStr">
+        <is>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+        </is>
+      </c>
+      <c r="D138" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+        </is>
+      </c>
+      <c r="E138" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F138" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G138" s="10" t="n"/>
+      <c r="H138" s="10" t="n"/>
+      <c r="I138" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J138" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="20" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C139" s="21" t="inlineStr">
+        <is>
+          <t>PSV-73 — Vytápění + komín</t>
+        </is>
+      </c>
+      <c r="D139" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+        </is>
+      </c>
+      <c r="E139" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F139" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G139" s="10" t="n"/>
+      <c r="H139" s="10" t="n"/>
+      <c r="I139" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J139" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="20" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C140" s="21" t="inlineStr">
+        <is>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+        </is>
+      </c>
+      <c r="D140" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+        </is>
+      </c>
+      <c r="E140" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F140" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G140" s="10" t="n"/>
+      <c r="H140" s="10" t="n"/>
+      <c r="I140" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J140" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C141" s="21" t="inlineStr">
+        <is>
+          <t>PSV-77 — Podlahy</t>
+        </is>
+      </c>
+      <c r="D141" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+        </is>
+      </c>
+      <c r="E141" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F141" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G141" s="10" t="n"/>
+      <c r="H141" s="10" t="n"/>
+      <c r="I141" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J141" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="20" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C142" s="21" t="inlineStr">
+        <is>
+          <t>PSV-78 — Povrchové úpravy</t>
+        </is>
+      </c>
+      <c r="D142" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+        </is>
+      </c>
+      <c r="E142" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F142" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G142" s="10" t="n"/>
+      <c r="H142" s="10" t="n"/>
+      <c r="I142" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J142" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="20" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C143" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D143" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E143" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F143" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G143" s="10" t="n"/>
+      <c r="H143" s="10" t="n"/>
+      <c r="I143" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J143" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="20" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C144" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D144" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E144" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F144" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G144" s="10" t="n"/>
+      <c r="H144" s="10" t="n"/>
+      <c r="I144" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J144" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J135"/>
+  <autoFilter ref="A1:J144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22423,11 +22785,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="55" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
@@ -23087,67 +23449,63 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>HSV-2 Základové a ŽB</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy sklad</t>
-        </is>
-      </c>
-      <c r="D10" s="27" t="inlineStr">
-        <is>
-          <t>271313??? ?</t>
+          <t>Trubka u pasu — vysoký pas</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
+          <t>Trubka Ø ~150 mm v štěrkovém obsypu podél vysokého pasu — drenáž/odvětrání radonu (OVĚŘIT)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G10" s="22" t="n">
-        <v>4.84</v>
+        <v>6.35</v>
       </c>
       <c r="H10" s="10" t="n"/>
       <c r="I10" s="10" t="n"/>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M10" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ + TZ statika sklad §4 — C16/20 XC0 pasy 500×500</t>
+          <t>řez A-A — kroužek trubky u pasu; účel + Ø NEpopsáno → OVĚŘIT</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O10" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P10" s="41" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
+          <t>#39</t>
+        </is>
+      </c>
+      <c r="O10" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P10" s="41" t="inlineStr"/>
       <c r="Q10" s="41" t="n"/>
     </row>
     <row r="11">
@@ -23156,55 +23514,55 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>HSV-2 Základové a ŽB</t>
+          <t>HSV-1 Zemní práce</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — spodní</t>
+          <t>Trubka u pasu — podél stěny</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
         <is>
-          <t>273313811</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
+          <t>Trubka Ø 120-130 mm v štěrkovém obsypu podél stěny — drenáž/odvětrání radonu (OVĚŘIT)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>6</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>6.01</v>
       </c>
       <c r="H11" s="10" t="n"/>
       <c r="I11" s="10" t="n"/>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="L11" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M11" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
+          <t>řez — druhá trubka u pasu; účel + Ø NEpopsáno → OVĚŘIT</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>#39</t>
         </is>
       </c>
       <c r="O11" s="26" t="inlineStr">
@@ -23212,12 +23570,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P11" s="41" t="n"/>
-      <c r="Q11" s="41" t="inlineStr">
-        <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P11" s="41" t="inlineStr"/>
+      <c r="Q11" s="41" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="20" t="n">
@@ -23230,26 +23584,26 @@
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — horní</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>311233812</t>
+          <t>Základové pasy sklad</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>271313??? ?</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Základové pasy z prostého betonu C16/20 XC0, 500×500 mm po obvodu skladu (nezámrzná hl.)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>6</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>4.84</v>
       </c>
       <c r="H12" s="10" t="n"/>
       <c r="I12" s="10" t="n"/>
@@ -23263,12 +23617,12 @@
       </c>
       <c r="L12" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
+          <t>DXF sklad_DPZ + TZ statika sklad §4 — C16/20 XC0 pasy 500×500</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -23276,17 +23630,17 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O12" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P12" s="41" t="n"/>
-      <c r="Q12" s="41" t="inlineStr">
-        <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
-        </is>
-      </c>
+      <c r="O12" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P12" s="41" t="inlineStr">
+        <is>
+          <t>S03a_sklad, S03b_sklad</t>
+        </is>
+      </c>
+      <c r="Q12" s="41" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
@@ -23299,26 +23653,26 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Beton patek + zídek — zalití</t>
+          <t>Patky parking — spodní</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
-          <t>273321321</t>
+          <t>273313811</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
+          <t>Dvoustupňové patky pro IPE180 zastřešení parkingu — spodní část prostý beton C16/20 500×500×500 mm × 6 ks</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>1.75</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>6</v>
       </c>
       <c r="H13" s="10" t="n"/>
       <c r="I13" s="10" t="n"/>
@@ -23328,21 +23682,21 @@
         </is>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M13" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 (6 patek)</t>
+          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O13" s="26" t="inlineStr">
@@ -23368,32 +23722,32 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože</t>
+          <t>Patky parking — horní</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>174101101</t>
+          <t>311233812</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
+          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
-        </is>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>1.76</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>6</v>
       </c>
       <c r="H14" s="10" t="n"/>
       <c r="I14" s="10" t="n"/>
       <c r="J14" s="8" t="inlineStr">
         <is>
-          <t>zemni_prace</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K14" s="24" t="n">
@@ -23401,12 +23755,12 @@
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
-          <t>matched_websearch_cross_discipline_legitimate</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t>DXF + TZ statika sklad</t>
+          <t>D.1.1.02 (6 patek + 6× IPE180 spočítáno na výkrese; rozteč 1000, řada 785+5×1000+435)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -23419,14 +23773,10 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P14" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad, S05_sklad</t>
-        </is>
-      </c>
+      <c r="P14" s="41" t="n"/>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>W1_PODLAHA_17.6_2026-06-01</t>
+          <t>PATKY_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23441,17 +23791,17 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Schodišťová deska + pas</t>
+          <t>Beton patek + zídek — zalití</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>273321321</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
+          <t>Beton C25/30 XC3 XF1 XA1 pro zalití tvarovek ZB patek + lemujících zídek parkingu</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -23460,7 +23810,7 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.8</v>
+        <v>1.75</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
@@ -23479,7 +23829,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — prefa schodové dílce + ŽB pas</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec 2 řady nad 6 patkami, šířka tvárnic 300 mm</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23492,12 +23842,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P15" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
-      <c r="Q15" s="41" t="n"/>
+      <c r="P15" s="41" t="n"/>
+      <c r="Q15" s="41" t="inlineStr">
+        <is>
+          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
@@ -23505,50 +23855,50 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna</t>
+          <t>Štěrkopískové lože</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>311233815</t>
+          <t>174101101</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+          <t>Štěrkopískové lože pod podlahu skladu + pod schodišťovou desku</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G16" s="23" t="n">
-        <v>18</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>1.76</v>
       </c>
       <c r="H16" s="10" t="n"/>
       <c r="I16" s="10" t="n"/>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zemni_prace</t>
         </is>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>matched_websearch_cross_discipline_legitimate</t>
         </is>
       </c>
       <c r="M16" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+          <t>DXF + TZ statika sklad</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -23563,12 +23913,12 @@
       </c>
       <c r="P16" s="41" t="inlineStr">
         <is>
-          <t>S04_sklad</t>
+          <t>S01_sklad, S05_sklad</t>
         </is>
       </c>
       <c r="Q16" s="41" t="inlineStr">
         <is>
-          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
+          <t>W1_PODLAHA_17.6_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23578,41 +23928,41 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu</t>
+          <t>Schodišťová deska + pas</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>311233811</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
+          <t>ŽB schodišťová deska ve sklonu + základový pas — beton C25/30 XC3 (terén ke skladu)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G17" s="22" t="n">
-        <v>62.5</v>
+        <v>0.8</v>
       </c>
       <c r="H17" s="10" t="n"/>
       <c r="I17" s="10" t="n"/>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K17" s="24" t="n">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="L17" s="20" t="inlineStr">
         <is>
@@ -23621,7 +23971,7 @@
       </c>
       <c r="M17" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
+          <t>TZ statika sklad §4 — prefa schodové dílce + ŽB pas</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -23636,14 +23986,10 @@
       </c>
       <c r="P17" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="Q17" s="41" t="inlineStr">
-        <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
-        </is>
-      </c>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q17" s="41" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="20" t="n">
@@ -23656,49 +24002,50 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>1875</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>18</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M18" s="8">
-        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
-        <v/>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M18" s="8" t="inlineStr">
+        <is>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+        </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O18" s="26" t="inlineStr">
@@ -23708,12 +24055,12 @@
       </c>
       <c r="P18" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S04_sklad</t>
         </is>
       </c>
       <c r="Q18" s="41" t="inlineStr">
         <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
+          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23728,17 +24075,17 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
+          <t>Tvarovky ZB obvod skladu</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311233811</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -23747,17 +24094,17 @@
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
@@ -23766,7 +24113,7 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -23781,12 +24128,12 @@
       </c>
       <c r="P19" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q19" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23801,50 +24148,49 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
+          <t>Výztuž ZB tvarovek</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G20" s="22" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04</t>
-        </is>
+          <t>family_verified_leaf_needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M20" s="8">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="O20" s="26" t="inlineStr">
@@ -23854,12 +24200,12 @@
       </c>
       <c r="P20" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q20" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23869,41 +24215,41 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>36.74</v>
+        <v>33</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
@@ -23912,7 +24258,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF DIMENSION</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -23927,12 +24273,12 @@
       </c>
       <c r="P21" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q21" s="41" t="inlineStr">
         <is>
-          <t>DS3_STROPNICE_11_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -23942,22 +24288,22 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -23966,17 +24312,17 @@
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>21.209</v>
+        <v>33</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
@@ -23985,7 +24331,7 @@
       </c>
       <c r="M22" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + DXF</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -24000,10 +24346,14 @@
       </c>
       <c r="P22" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
-        </is>
-      </c>
-      <c r="Q22" s="41" t="n"/>
+          <t>S03a_sklad, S04_sklad</t>
+        </is>
+      </c>
+      <c r="Q22" s="41" t="inlineStr">
+        <is>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="20" t="n">
@@ -24016,36 +24366,36 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>22.26945</v>
+        <v>31</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
@@ -24054,7 +24404,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 — HI souvrství</t>
+          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -24072,7 +24422,11 @@
           <t>S02_sklad</t>
         </is>
       </c>
-      <c r="Q23" s="41" t="n"/>
+      <c r="Q23" s="41" t="inlineStr">
+        <is>
+          <t>TRAMY_10ks_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="20" t="n">
@@ -24085,50 +24439,49 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
-        <is>
-          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
-        </is>
+      <c r="M24" s="8">
+        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
+        <v/>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O24" s="26" t="inlineStr">
@@ -24143,7 +24496,7 @@
       </c>
       <c r="Q24" s="41" t="inlineStr">
         <is>
-          <t>IPE_7to6_DRAWING_2026-06-01</t>
+          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24158,17 +24511,17 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -24177,27 +24530,26 @@
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L25" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M25" s="8" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
-        </is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M25" s="8">
+        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
+        <v/>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -24216,7 +24568,7 @@
       </c>
       <c r="Q25" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>HI_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24231,17 +24583,17 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -24250,7 +24602,7 @@
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
@@ -24260,20 +24612,21 @@
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M26" s="8">
-        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
-        <v/>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+        </is>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O26" s="26" t="inlineStr">
@@ -24298,22 +24651,22 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště prefa</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Sklad mezipodesta schodiště — prefa betonové stupně (9 ks × 179.5×250 mm) + kladecí vrstva zavlhlého betonu nad ŽB podkladní deskou (S05 sklad skladba)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -24322,26 +24675,26 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M27" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N27" s="20" t="inlineStr">
@@ -24356,12 +24709,12 @@
       </c>
       <c r="P27" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q27" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -24371,49 +24724,50 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Napojení vjezdu na ulici Dvořákova — vydláždění z betonových dlaždic + spádování na pozemek investora + odvodnění dešťové vody na pozemek (ne na komunikaci)</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="G28" s="22" t="n"/>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="G28" s="22" t="n">
+        <v>1420</v>
+      </c>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR požadavek</t>
-        </is>
+      <c r="M28" s="8">
+        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
+        <v/>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
@@ -24425,10 +24779,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P28" s="41" t="inlineStr"/>
+      <c r="P28" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
       <c r="Q28" s="41" t="inlineStr">
         <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+          <t>IPE_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24438,41 +24796,41 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Schodiště prefa stupně</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G29" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G29" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.85</v>
+        <v>0.95</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
@@ -24481,7 +24839,7 @@
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24494,8 +24852,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P29" s="41" t="n"/>
-      <c r="Q29" s="41" t="n"/>
+      <c r="P29" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q29" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="20" t="n">
@@ -24503,12 +24869,12 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Oplocení (plot)</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -24518,26 +24884,26 @@
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
@@ -24546,12 +24912,12 @@
       </c>
       <c r="M30" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
+          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
         </is>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
-          <t>#37</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O30" s="26" t="inlineStr">
@@ -24560,7 +24926,11 @@
         </is>
       </c>
       <c r="P30" s="41" t="inlineStr"/>
-      <c r="Q30" s="41" t="n"/>
+      <c r="Q30" s="41" t="inlineStr">
+        <is>
+          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="20" t="n">
@@ -24568,41 +24938,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí stání</t>
+          <t>Vjezd — pískové lože</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564751111</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>18.5</v>
+        <v>0.28</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -24611,12 +24981,12 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
         <is>
-          <t>#38</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O31" s="26" t="inlineStr">
@@ -24633,41 +25003,41 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Vjezd — štěrkový podklad</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564861111</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G32" s="23" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G32" s="22" t="n">
+        <v>1.05</v>
       </c>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="L32" s="20" t="inlineStr">
         <is>
@@ -24676,7 +25046,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -24690,11 +25060,7 @@
         </is>
       </c>
       <c r="P32" s="41" t="inlineStr"/>
-      <c r="Q32" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="Q32" s="41" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n">
@@ -24702,50 +25068,50 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D33" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Odvodňovací žlab</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>23.6</v>
+        <v>7.775</v>
       </c>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K33" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L33" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
+          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -24753,21 +25119,13 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O33" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P33" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q33" s="41" t="inlineStr">
-        <is>
-          <t>S01_AREA_23.6_2026-06-01</t>
-        </is>
-      </c>
+      <c r="O33" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P33" s="41" t="inlineStr"/>
+      <c r="Q33" s="41" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="20" t="n">
@@ -24775,41 +25133,41 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Odvodňovací žlab — podkladní beton</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>273321411</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G34" s="23" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>0.47</v>
       </c>
       <c r="H34" s="10" t="n"/>
       <c r="I34" s="10" t="n"/>
       <c r="J34" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K34" s="24" t="n">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="L34" s="20" t="inlineStr">
         <is>
@@ -24818,7 +25176,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -24831,7 +25189,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P34" s="41" t="n"/>
+      <c r="P34" s="41" t="inlineStr"/>
       <c r="Q34" s="41" t="n"/>
     </row>
     <row r="35">
@@ -24840,41 +25198,41 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
+          <t>Okapový žlab</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
         <is>
-          <t>997013211</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n"/>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K35" s="24" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="L35" s="20" t="inlineStr">
         <is>
@@ -24883,7 +25241,7 @@
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -24896,7 +25254,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P35" s="41" t="n"/>
+      <c r="P35" s="41" t="inlineStr"/>
       <c r="Q35" s="41" t="n"/>
     </row>
     <row r="36">
@@ -24905,41 +25263,41 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Schodiště — podkladní deska</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>273313611</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="G36" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G36" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H36" s="10" t="n"/>
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K36" s="24" t="n">
-        <v>0.99</v>
+        <v>0.7</v>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
@@ -24948,12 +25306,12 @@
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>skladba S05 — podkladní betonová deska</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O36" s="26" t="inlineStr">
@@ -24961,7 +25319,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P36" s="41" t="n"/>
+      <c r="P36" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q36" s="41" t="n"/>
     </row>
     <row r="37">
@@ -24970,12 +25332,12 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+          <t>Schodiště — kladecí beton</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -24985,22 +25347,22 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G37" s="23" t="n">
-        <v>1</v>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>0.28</v>
       </c>
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="10" t="n"/>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K37" s="24" t="n">
@@ -25013,12 +25375,12 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O37" s="26" t="inlineStr">
@@ -25026,12 +25388,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P37" s="41" t="inlineStr"/>
-      <c r="Q37" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P37" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q37" s="41" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="20" t="n">
@@ -25039,27 +25401,27 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G38" s="23" t="n">
@@ -25069,11 +25431,11 @@
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
@@ -25082,7 +25444,7 @@
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
@@ -25098,9 +25460,610 @@
       <c r="P38" s="41" t="n"/>
       <c r="Q38" s="41" t="n"/>
     </row>
+    <row r="39">
+      <c r="A39" s="20" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Oplocení (plot)</t>
+        </is>
+      </c>
+      <c r="D39" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="F39" s="20" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="H39" s="10" t="n"/>
+      <c r="I39" s="10" t="n"/>
+      <c r="J39" s="8" t="inlineStr">
+        <is>
+          <t>zamecnik</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="N39" s="20" t="inlineStr">
+        <is>
+          <t>#37</t>
+        </is>
+      </c>
+      <c r="O39" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P39" s="41" t="inlineStr"/>
+      <c r="Q39" s="41" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnické konstrukce</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="inlineStr">
+        <is>
+          <t>Zábradlí stání</t>
+        </is>
+      </c>
+      <c r="D40" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+        </is>
+      </c>
+      <c r="F40" s="20" t="inlineStr">
+        <is>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="10" t="n"/>
+      <c r="J40" s="8" t="inlineStr">
+        <is>
+          <t>zamecnik</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L40" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+        </is>
+      </c>
+      <c r="N40" s="20" t="inlineStr">
+        <is>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="O40" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P40" s="41" t="inlineStr"/>
+      <c r="Q40" s="41" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="20" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="8" t="inlineStr">
+        <is>
+          <t>PSV-76 Zámečnictví</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Vjezdová brána</t>
+        </is>
+      </c>
+      <c r="D41" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+        </is>
+      </c>
+      <c r="F41" s="20" t="inlineStr">
+        <is>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G41" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="10" t="n"/>
+      <c r="I41" s="10" t="n"/>
+      <c r="J41" s="8" t="inlineStr">
+        <is>
+          <t>zamecnik</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M41" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01)</t>
+        </is>
+      </c>
+      <c r="N41" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O41" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P41" s="41" t="inlineStr"/>
+      <c r="Q41" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="20" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="8" t="inlineStr">
+        <is>
+          <t>PSV-77 Podlahy</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D42" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+        </is>
+      </c>
+      <c r="F42" s="20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G42" s="22" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H42" s="10" t="n"/>
+      <c r="I42" s="10" t="n"/>
+      <c r="J42" s="8" t="inlineStr">
+        <is>
+          <t>podlahar</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L42" s="20" t="inlineStr">
+        <is>
+          <t>wrong_leaf_disambiguation_needed</t>
+        </is>
+      </c>
+      <c r="M42" s="8" t="inlineStr">
+        <is>
+          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
+        </is>
+      </c>
+      <c r="N42" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O42" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P42" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q42" s="41" t="inlineStr">
+        <is>
+          <t>S01_AREA_23.6_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+        </is>
+      </c>
+      <c r="D43" s="20" t="inlineStr">
+        <is>
+          <t>031032000</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+        </is>
+      </c>
+      <c r="F43" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G43" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="10" t="n"/>
+      <c r="I43" s="10" t="n"/>
+      <c r="J43" s="8" t="inlineStr">
+        <is>
+          <t>prefa_bloky_specialista</t>
+        </is>
+      </c>
+      <c r="K43" s="24" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L43" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M43" s="8" t="inlineStr">
+        <is>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+        </is>
+      </c>
+      <c r="N43" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O43" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P43" s="41" t="n"/>
+      <c r="Q43" s="41" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="20" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Doprava + odpad</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace odpadu sklad</t>
+        </is>
+      </c>
+      <c r="D44" s="20" t="inlineStr">
+        <is>
+          <t>997013211</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+        </is>
+      </c>
+      <c r="F44" s="20" t="inlineStr">
+        <is>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G44" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="H44" s="10" t="n"/>
+      <c r="I44" s="10" t="n"/>
+      <c r="J44" s="8" t="inlineStr">
+        <is>
+          <t>bourani_demolice</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M44" s="8" t="inlineStr">
+        <is>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+        </is>
+      </c>
+      <c r="N44" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O44" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P44" s="41" t="n"/>
+      <c r="Q44" s="41" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="20" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad</t>
+        </is>
+      </c>
+      <c r="D45" s="20" t="inlineStr">
+        <is>
+          <t>030141000</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+        </is>
+      </c>
+      <c r="F45" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="G45" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="10" t="n"/>
+      <c r="I45" s="10" t="n"/>
+      <c r="J45" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="inlineStr">
+        <is>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+        </is>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O45" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P45" s="41" t="n"/>
+      <c r="Q45" s="41" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="20" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C46" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F46" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G46" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="10" t="n"/>
+      <c r="I46" s="10" t="n"/>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O46" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P46" s="41" t="inlineStr"/>
+      <c r="Q46" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F47" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G47" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="10" t="n"/>
+      <c r="I47" s="10" t="n"/>
+      <c r="J47" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M47" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N47" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O47" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P47" s="41" t="n"/>
+      <c r="Q47" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O38"/>
-  <conditionalFormatting sqref="K2:K38">
+  <autoFilter ref="A1:O47"/>
+  <conditionalFormatting sqref="K2:K47">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
@@ -4406,7 +4406,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — horní — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking — horní — Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -23732,7 +23732,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -23776,7 +23776,7 @@
       <c r="P14" s="41" t="n"/>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+          <t>TVARNICE_SPLIT_FIX_2026-06-02 — materiál-leg byl chybně ocel S235 (auto-split chytil IPE180); ztracené bednění → komplet</t>
         </is>
       </c>
     </row>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (130 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 143 řádků.</t>
+          <t>HSV položkově (132 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 145 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 46 sklad = 247 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 48 sklad = 249 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>247 (201 dum + 46 sklad)</t>
+          <t>249 (201 dum + 48 sklad)</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 130 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
+          <t>HSV 132 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 9 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
+          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 11 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 170 needs_production_lookup (68.8 %)</t>
+          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 172 needs_production_lookup (69.1 %)</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>37 items (viz Otazky_pro_Karla docx)</t>
+          <t>38 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1186,8 +1186,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-247 položek celkem (201 dum + 46 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 9×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
+249 položek celkem (201 dum + 48 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 11×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -2987,11 +2987,11 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy sklad; Patky parking — spodní; Patky parking — horní; Beton patek + zídek — zalití; … (+2 dalších)</t>
+          <t>Základové pasy sklad; Patky parking — spodní; Patky parking — horní; Beton patek + zídek — zalití; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="10" t="n"/>
@@ -3163,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
@@ -8431,34 +8431,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C132" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
+          <t>Bednění základů (pasy + patky spodní) — Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F132" s="22" t="n">
+        <v>25.4</v>
       </c>
       <c r="G132" s="10" t="n"/>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273351215</t>
         </is>
       </c>
     </row>
@@ -8471,34 +8471,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C133" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Výztuž tvárnic ZB patek + věnce — Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="n">
-        <v>1</v>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>153</v>
       </c>
       <c r="G133" s="10" t="n"/>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zelezarsky</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273361821</t>
         </is>
       </c>
     </row>
@@ -8513,12 +8513,12 @@
       </c>
       <c r="C134" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
@@ -8548,17 +8548,17 @@
       </c>
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C135" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E135" s="20" t="inlineStr">
@@ -8588,17 +8588,17 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C136" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="C137" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E137" s="20" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="C138" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E138" s="20" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="C139" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E139" s="20" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="C140" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="C141" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E141" s="20" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="C142" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E142" s="20" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="C143" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E143" s="20" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="C144" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E144" s="20" t="inlineStr">
@@ -8942,8 +8942,88 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="20" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C145" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E145" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="10" t="n"/>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J145" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C146" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="10" t="n"/>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J146" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J144"/>
+  <autoFilter ref="A1:J146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22785,7 +22865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23810,7 +23890,7 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
@@ -23829,7 +23909,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec 2 řady nad 6 patkami, šířka tvárnic 300 mm</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec délka 6.7 m (ruční obmer)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23845,7 +23925,7 @@
       <c r="P15" s="41" t="n"/>
       <c r="Q15" s="41" t="inlineStr">
         <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+          <t>VENEC_6.7_2026-06-02</t>
         </is>
       </c>
     </row>
@@ -23997,41 +24077,41 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna</t>
+          <t>Bednění základů (pasy + patky spodní)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>311233815</t>
+          <t>273351215</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+          <t>Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>18</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>25.4</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
@@ -24040,12 +24120,12 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+          <t>výkres D.1.1.02 + řez — bednění základů; podíl do rýhy vs systémové OVĚŘIT</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#42</t>
         </is>
       </c>
       <c r="O18" s="26" t="inlineStr">
@@ -24053,16 +24133,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P18" s="41" t="inlineStr">
-        <is>
-          <t>S04_sklad</t>
-        </is>
-      </c>
-      <c r="Q18" s="41" t="inlineStr">
-        <is>
-          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P18" s="41" t="inlineStr"/>
+      <c r="Q18" s="41" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -24070,41 +24142,41 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu</t>
+          <t>Výztuž tvárnic ZB patek + věnce</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>311233811</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
+          <t>Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>62.5</v>
+        <v>153</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>zelezarsky</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
@@ -24113,12 +24185,12 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
+          <t>TZ statika sklad §3 — výztuž B500B do tvárnic ZB; sazba dle stěny S03a (HSV3.003)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#42</t>
         </is>
       </c>
       <c r="O19" s="26" t="inlineStr">
@@ -24126,16 +24198,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P19" s="41" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="Q19" s="41" t="inlineStr">
-        <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P19" s="41" t="inlineStr"/>
+      <c r="Q19" s="41" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -24148,49 +24212,50 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>1875</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>18</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M20" s="8">
-        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
-        <v/>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+        </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O20" s="26" t="inlineStr">
@@ -24200,12 +24265,12 @@
       </c>
       <c r="P20" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S04_sklad</t>
         </is>
       </c>
       <c r="Q20" s="41" t="inlineStr">
         <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
+          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24220,17 +24285,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
+          <t>Tvarovky ZB obvod skladu</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311233811</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -24239,17 +24304,17 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
@@ -24258,7 +24323,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -24273,12 +24338,12 @@
       </c>
       <c r="P21" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q21" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24293,50 +24358,49 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
+          <t>Výztuž ZB tvarovek</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04</t>
-        </is>
+          <t>family_verified_leaf_needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M22" s="8">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="O22" s="26" t="inlineStr">
@@ -24346,12 +24410,12 @@
       </c>
       <c r="P22" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q22" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24361,41 +24425,41 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
@@ -24404,7 +24468,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -24419,12 +24483,12 @@
       </c>
       <c r="P23" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q23" s="41" t="inlineStr">
         <is>
-          <t>TRAMY_10ks_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24434,22 +24498,22 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -24458,26 +24522,27 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>18.1</v>
+        <v>33</v>
       </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M24" s="8">
-        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
-        <v/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
+        </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
@@ -24491,12 +24556,12 @@
       </c>
       <c r="P24" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q24" s="41" t="inlineStr">
         <is>
-          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24511,32 +24576,32 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
@@ -24547,9 +24612,10 @@
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M25" s="8">
-        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
-        <v/>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
+        </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -24568,7 +24634,7 @@
       </c>
       <c r="Q25" s="41" t="inlineStr">
         <is>
-          <t>HI_TRAMY_BASE_2026-06-01</t>
+          <t>TRAMY_10ks_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24583,50 +24649,49 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
-        </is>
+      <c r="M26" s="8">
+        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
+        <v/>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O26" s="26" t="inlineStr">
@@ -24641,7 +24706,7 @@
       </c>
       <c r="Q26" s="41" t="inlineStr">
         <is>
-          <t>IPE_7to6_DRAWING_2026-06-01</t>
+          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24656,17 +24721,17 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -24675,27 +24740,26 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
-        </is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M27" s="8">
+        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
+        <v/>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -24714,7 +24778,7 @@
       </c>
       <c r="Q27" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>HI_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24729,17 +24793,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -24748,7 +24812,7 @@
         </is>
       </c>
       <c r="G28" s="22" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
@@ -24758,20 +24822,21 @@
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M28" s="8">
-        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
-        <v/>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+        </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O28" s="26" t="inlineStr">
@@ -24796,22 +24861,22 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Schodiště prefa stupně</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -24820,26 +24885,26 @@
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24854,12 +24919,12 @@
       </c>
       <c r="P29" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q29" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -24869,51 +24934,50 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>7</v>
+        <v>1420</v>
       </c>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
-        </is>
+      <c r="M30" s="8">
+        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
+        <v/>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -24925,10 +24989,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P30" s="41" t="inlineStr"/>
+      <c r="P30" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
       <c r="Q30" s="41" t="inlineStr">
         <is>
-          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+          <t>IPE_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24938,41 +25006,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + zpevněné plochy</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Vjezd — pískové lože</t>
+          <t>Schodiště prefa stupně</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>564751111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>0.28</v>
+        <v>5.5</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -24981,7 +25049,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -24994,8 +25062,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P31" s="41" t="inlineStr"/>
-      <c r="Q31" s="41" t="n"/>
+      <c r="P31" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q31" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="n">
@@ -25003,37 +25079,37 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + zpevněné plochy</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Vjezd — štěrkový podklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>564861111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
+          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
@@ -25046,7 +25122,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -25060,7 +25136,11 @@
         </is>
       </c>
       <c r="P32" s="41" t="inlineStr"/>
-      <c r="Q32" s="41" t="n"/>
+      <c r="Q32" s="41" t="inlineStr">
+        <is>
+          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n">
@@ -25073,26 +25153,26 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Odvodňovací žlab</t>
+          <t>Vjezd — pískové lože</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564751111</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>7.775</v>
+        <v>0.28</v>
       </c>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
@@ -25111,7 +25191,7 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -25138,17 +25218,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Odvodňovací žlab — podkladní beton</t>
+          <t>Vjezd — štěrkový podklad</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>273321411</t>
+          <t>564861111</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -25157,7 +25237,7 @@
         </is>
       </c>
       <c r="G34" s="22" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="H34" s="10" t="n"/>
       <c r="I34" s="10" t="n"/>
@@ -25176,7 +25256,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -25203,7 +25283,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Okapový žlab</t>
+          <t>Odvodňovací žlab</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -25213,7 +25293,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -25222,7 +25302,7 @@
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>6</v>
+        <v>7.775</v>
       </c>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n"/>
@@ -25232,7 +25312,7 @@
         </is>
       </c>
       <c r="K35" s="24" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="L35" s="20" t="inlineStr">
         <is>
@@ -25241,7 +25321,7 @@
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
+          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -25268,36 +25348,36 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Schodiště — podkladní deska</t>
+          <t>Odvodňovací žlab — podkladní beton</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>273313611</t>
+          <t>273321411</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Podkladní betonová deska pod prefa schodiště S05</t>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G36" s="22" t="n">
-        <v>5.5</v>
+        <v>0.47</v>
       </c>
       <c r="H36" s="10" t="n"/>
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K36" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
@@ -25306,12 +25386,12 @@
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>skladba S05 — podkladní betonová deska</t>
+          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O36" s="26" t="inlineStr">
@@ -25319,11 +25399,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P36" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="P36" s="41" t="inlineStr"/>
       <c r="Q36" s="41" t="n"/>
     </row>
     <row r="37">
@@ -25337,7 +25413,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Schodiště — kladecí beton</t>
+          <t>Okapový žlab</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -25347,16 +25423,16 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>0.28</v>
+        <v>6</v>
       </c>
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="10" t="n"/>
@@ -25366,7 +25442,7 @@
         </is>
       </c>
       <c r="K37" s="24" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="L37" s="20" t="inlineStr">
         <is>
@@ -25375,12 +25451,12 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
+          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O37" s="26" t="inlineStr">
@@ -25388,11 +25464,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P37" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="P37" s="41" t="inlineStr"/>
       <c r="Q37" s="41" t="n"/>
     </row>
     <row r="38">
@@ -25401,41 +25473,41 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Schodiště — podkladní deska</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>273313611</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H38" s="10" t="n"/>
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
@@ -25444,12 +25516,12 @@
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>skladba S05 — podkladní betonová deska</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O38" s="26" t="inlineStr">
@@ -25457,7 +25529,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P38" s="41" t="n"/>
+      <c r="P38" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q38" s="41" t="n"/>
     </row>
     <row r="39">
@@ -25466,12 +25542,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Oplocení (plot)</t>
+          <t>Schodiště — kladecí beton</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -25481,22 +25557,22 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G39" s="22" t="n">
-        <v>3.8</v>
+        <v>0.28</v>
       </c>
       <c r="H39" s="10" t="n"/>
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K39" s="24" t="n">
@@ -25509,12 +25585,12 @@
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
+          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>#37</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O39" s="26" t="inlineStr">
@@ -25522,7 +25598,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P39" s="41" t="inlineStr"/>
+      <c r="P39" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q39" s="41" t="n"/>
     </row>
     <row r="40">
@@ -25531,41 +25611,41 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí stání</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="n">
-        <v>18.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H40" s="10" t="n"/>
       <c r="I40" s="10" t="n"/>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K40" s="24" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="L40" s="20" t="inlineStr">
         <is>
@@ -25574,12 +25654,12 @@
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>#38</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O40" s="26" t="inlineStr">
@@ -25587,7 +25667,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P40" s="41" t="inlineStr"/>
+      <c r="P40" s="41" t="n"/>
       <c r="Q40" s="41" t="n"/>
     </row>
     <row r="41">
@@ -25596,12 +25676,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Oplocení (plot)</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -25611,16 +25691,16 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>3.8</v>
       </c>
       <c r="H41" s="10" t="n"/>
       <c r="I41" s="10" t="n"/>
@@ -25630,7 +25710,7 @@
         </is>
       </c>
       <c r="K41" s="24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L41" s="20" t="inlineStr">
         <is>
@@ -25639,12 +25719,12 @@
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#37</t>
         </is>
       </c>
       <c r="O41" s="26" t="inlineStr">
@@ -25653,11 +25733,7 @@
         </is>
       </c>
       <c r="P41" s="41" t="inlineStr"/>
-      <c r="Q41" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="Q41" s="41" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
@@ -25665,72 +25741,64 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D42" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Zábradlí stání</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G42" s="22" t="n">
-        <v>23.6</v>
+        <v>18.5</v>
       </c>
       <c r="H42" s="10" t="n"/>
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K42" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O42" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P42" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q42" s="41" t="inlineStr">
-        <is>
-          <t>S01_AREA_23.6_2026-06-01</t>
-        </is>
-      </c>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="O42" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P42" s="41" t="inlineStr"/>
+      <c r="Q42" s="41" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
@@ -25738,27 +25806,27 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
@@ -25768,11 +25836,11 @@
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K43" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L43" s="20" t="inlineStr">
         <is>
@@ -25781,7 +25849,7 @@
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N43" s="20" t="inlineStr">
@@ -25794,8 +25862,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P43" s="41" t="n"/>
-      <c r="Q43" s="41" t="n"/>
+      <c r="P43" s="41" t="inlineStr"/>
+      <c r="Q43" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
@@ -25803,50 +25875,50 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G44" s="22" t="n">
-        <v>8</v>
+        <v>23.6</v>
       </c>
       <c r="H44" s="10" t="n"/>
       <c r="I44" s="10" t="n"/>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K44" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L44" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
         </is>
       </c>
       <c r="N44" s="20" t="inlineStr">
@@ -25854,13 +25926,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O44" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P44" s="41" t="n"/>
-      <c r="Q44" s="41" t="n"/>
+      <c r="O44" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P44" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q44" s="41" t="inlineStr">
+        <is>
+          <t>S01_AREA_23.6_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="n">
@@ -25868,22 +25948,22 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
@@ -25898,11 +25978,11 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K45" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
@@ -25911,7 +25991,7 @@
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
@@ -25933,41 +26013,41 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H46" s="10" t="n"/>
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K46" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
@@ -25976,7 +26056,7 @@
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
@@ -25989,12 +26069,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P46" s="41" t="inlineStr"/>
-      <c r="Q46" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P46" s="41" t="n"/>
+      <c r="Q46" s="41" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="20" t="n">
@@ -26002,27 +26078,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Geodetické vytýčení sklad</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
@@ -26032,11 +26108,11 @@
       <c r="I47" s="10" t="n"/>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K47" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L47" s="20" t="inlineStr">
         <is>
@@ -26045,7 +26121,7 @@
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
@@ -26061,9 +26137,143 @@
       <c r="P47" s="41" t="n"/>
       <c r="Q47" s="41" t="n"/>
     </row>
+    <row r="48">
+      <c r="A48" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L48" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O48" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P48" s="41" t="inlineStr"/>
+      <c r="Q48" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K49" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O49" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P49" s="41" t="n"/>
+      <c r="Q49" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O47"/>
-  <conditionalFormatting sqref="K2:K47">
+  <autoFilter ref="A1:O49"/>
+  <conditionalFormatting sqref="K2:K49">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>

--- a/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
+++ b/test-data/RD_Jachymov_dum/outputs/Vykaz_vymer_RD_Jachymov_VSE_VARIANTY_2026-06-02_v2.xlsx
@@ -21,9 +21,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Var_A_Agregovany_Dum'!$A$1:$G$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Var_A_Agregovany_Sklad'!$A$1:$G$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Var_C_Hybrid'!$A$1:$J$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Var_B_Polozkovy_Dum'!$A$1:$O$202</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Var_B_Polozkovy_Sklad'!$A$1:$O$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Var_F_URS_Verification_Trail'!$A$1:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1009,11 +1009,11 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV položkově (130 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 143 řádků.</t>
+          <t>HSV položkově (132 ks) + PSV/TZB/VRN agregovaně (13 skupin) = 145 řádků.</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D24" s="10" t="n"/>
       <c r="E24" s="10" t="n"/>
@@ -1027,11 +1027,11 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Plný detail (201 dum + 46 sklad = 247 položek). Cílový rozsah pro produkční pricing.</t>
+          <t>Plný detail (201 dum + 48 sklad = 249 položek). Cílový rozsah pro produkční pricing.</t>
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D25" s="10" t="n"/>
       <c r="E25" s="10" t="n"/>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>247 (201 dum + 46 sklad)</t>
+          <t>249 (201 dum + 48 sklad)</t>
         </is>
       </c>
     </row>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>HSV 130 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
+          <t>HSV 132 | M 2 | PSV 58 | TZB 34 | VRN 23</t>
         </is>
       </c>
     </row>
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 9 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
+          <t>0.99: 17 | 0.95: 29 | 0.90: 32 | 0.85: 48 | 0.80: 21 | 0.75: 75 | 0.70: 11 | 0.65: 1 | 0.60: 5 | 0.50: 6 | 0.00: 4</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 170 needs_production_lookup (68.8 %)</t>
+          <t>8 WebSearch verified (3.2 %) ✓ | 5 wrong leaf flagged (2.0 %) ⚠ | 172 needs_production_lookup (69.1 %)</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>37 items (viz Otazky_pro_Karla docx)</t>
+          <t>38 items (viz Otazky_pro_Karla docx)</t>
         </is>
       </c>
     </row>
@@ -1186,8 +1186,8 @@
       <c r="A43" s="12" t="inlineStr">
         <is>
           <t>Rozpočet generován STAVAGENT pipelinem z DSP dokumentace s DPS-grade DXF metadaty.
-247 položek celkem (201 dum + 46 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
-Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 9×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
+249 položek celkem (201 dum + 48 sklad), 4 corpus patterns aplikované, zero-fabrication policy.
+Confidence distribution: 17×0.99 · 29×0.95 · 32×0.90 · 48×0.85 · 21×0.80 · 75×0.75 · 11×0.70 · 1×0.65 · 5×0.60 · 6×0.50 · 4×0.00.
 25 položek vzniklo per-room expansion ze 9 aggregate parents (každá expanded položka tagged _expansion_origin).
 9 položek recalculated s exact external perimeter 38.70 m (DXF km_R_návrh_tlustá 2 closed polygon) vs prior fallback 41.0 m.
 Skladby vrstev (Sheet 8 Var_E) pochází POUZE z TZ explicit text + DXF cross-validation HATCH patterns. ŽÁDNÉ generic 'standardní RD' assumption — kde TZ silent, explicit fallback flag s ČSN default.
@@ -2987,11 +2987,11 @@
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>Základové pasy sklad; Patky parking — spodní; Patky parking — horní; Beton patek + zídek — zalití; … (+2 dalších)</t>
+          <t>Základové pasy sklad; Patky parking — spodní; Patky parking — horní; Beton patek + zídek — zalití; … (+4 dalších)</t>
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" s="10" t="n"/>
       <c r="F3" s="10" t="n"/>
@@ -3163,7 +3163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>Patky parking — horní — Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking — horní — Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="F32" s="22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n"/>
@@ -8431,34 +8431,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C132" s="21" t="inlineStr">
-        <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+      <c r="C132" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
+          <t>Bednění základů (pasy + patky spodní) — Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
         </is>
       </c>
       <c r="E132" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F132" s="9" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="F132" s="22" t="n">
+        <v>25.4</v>
       </c>
       <c r="G132" s="10" t="n"/>
       <c r="H132" s="10" t="n"/>
       <c r="I132" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="J132" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273351215</t>
         </is>
       </c>
     </row>
@@ -8471,34 +8471,34 @@
           <t>260217_sklad</t>
         </is>
       </c>
-      <c r="C133" s="21" t="inlineStr">
-        <is>
-          <t>PSV-77 — Podlahy</t>
+      <c r="C133" s="8" t="inlineStr">
+        <is>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
+          <t>Výztuž tvárnic ZB patek + věnce — Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
         </is>
       </c>
       <c r="E133" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
-        </is>
-      </c>
-      <c r="F133" s="9" t="n">
-        <v>1</v>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="F133" s="22" t="n">
+        <v>153</v>
       </c>
       <c r="G133" s="10" t="n"/>
       <c r="H133" s="10" t="n"/>
       <c r="I133" s="8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>zelezarsky</t>
         </is>
       </c>
       <c r="J133" s="8" t="inlineStr">
         <is>
-          <t>agregát</t>
+          <t>URS-prop 273361821</t>
         </is>
       </c>
     </row>
@@ -8513,12 +8513,12 @@
       </c>
       <c r="C134" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
+          <t>[agregát] 4 položek: Bezpečnostní dveře RC3 sklad; Vjezdová brána; Oplocení (plot); … (+1 dalších)</t>
         </is>
       </c>
       <c r="E134" s="20" t="inlineStr">
@@ -8548,17 +8548,17 @@
       </c>
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C135" s="21" t="inlineStr">
         <is>
-          <t>M-21 — Elektroinstalace silnoproudá</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
+          <t>[agregát] 1 položek: Betonová dlažba sklad</t>
         </is>
       </c>
       <c r="E135" s="20" t="inlineStr">
@@ -8588,17 +8588,17 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>260219_dum</t>
+          <t>260217_sklad</t>
         </is>
       </c>
       <c r="C136" s="21" t="inlineStr">
         <is>
-          <t>M-24</t>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
+          <t>[agregát] 5 položek: Doprava prefa H-BLOK auto s hyd. rukou; Likvidace odpadu sklad; Geodetické vytýčení sklad; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E136" s="20" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="C137" s="21" t="inlineStr">
         <is>
-          <t>PSV-71 — Izolace HI + TI</t>
+          <t>M-21 — Elektroinstalace silnoproudá</t>
         </is>
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
+          <t>[agregát] 8 položek: Demontáž stávající ELI; Pojistková skříň + 3× podružný rozvaděč; Rozvody silnoproud; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E137" s="20" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="C138" s="21" t="inlineStr">
         <is>
-          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
+          <t>M-24</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
+          <t>[agregát] 1 položek: Lokální odtah digestoří kuchyní</t>
         </is>
       </c>
       <c r="E138" s="20" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="C139" s="21" t="inlineStr">
         <is>
-          <t>PSV-73 — Vytápění + komín</t>
+          <t>PSV-71 — Izolace HI + TI</t>
         </is>
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
+          <t>[agregát] 5 položek: HI pod ŽB deskou 1.NP; Odvětrání radonu z podloží; HI koupelny 1.NP + 2.NP + 3.NP; … (+2 dalších)</t>
         </is>
       </c>
       <c r="E139" s="20" t="inlineStr">
@@ -8753,12 +8753,12 @@
       </c>
       <c r="C140" s="21" t="inlineStr">
         <is>
-          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
+          <t>PSV-72 — ZTI (vodovod + kanalizace + sanita)</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
+          <t>[agregát] 19 položek: Revize stávajících přípojek; Nové rozvody vody do 3.NP; Nové odpadní rozvody; … (+16 dalších)</t>
         </is>
       </c>
       <c r="E140" s="20" t="inlineStr">
@@ -8793,12 +8793,12 @@
       </c>
       <c r="C141" s="21" t="inlineStr">
         <is>
-          <t>PSV-77 — Podlahy</t>
+          <t>PSV-73 — Vytápění + komín</t>
         </is>
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
+          <t>[agregát] 8 položek: Sporáková kamna na tuhá paliva; Sporáková kamna — montáž; Elektrokotel 3.NP; … (+5 dalších)</t>
         </is>
       </c>
       <c r="E141" s="20" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="C142" s="21" t="inlineStr">
         <is>
-          <t>PSV-78 — Povrchové úpravy</t>
+          <t>PSV-76 — Výplně otvorů + klempířina + zámečnictví + truhlář</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
+          <t>[agregát] 22 položek: Plastové okno trojsklo — 'okno 1.NP' (ulice); Plastové okno trojsklo — 'okno 1.NP vzadu' (zahrada); Plastové okno trojsklo — 'okno 2.NP' (ulice); … (+19 dalších)</t>
         </is>
       </c>
       <c r="E142" s="20" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="C143" s="21" t="inlineStr">
         <is>
-          <t>PSV-95 — Detekce požární</t>
+          <t>PSV-77 — Podlahy</t>
         </is>
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+          <t>[agregát] 7 položek: Nášlap vinyl obytné místnosti; Nášlap keramická dlažba — mokré zóny; Nášlap keramická dlažba — 1.PP sklep; … (+4 dalších)</t>
         </is>
       </c>
       <c r="E143" s="20" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="C144" s="21" t="inlineStr">
         <is>
-          <t>VRN — Vedlejší rozpočtové náklady</t>
+          <t>PSV-78 — Povrchové úpravy</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+          <t>[agregát] 16 položek: Omítka jádrová + štuk 1.PP; Omítka jádrová + štuk 1.NP; Omítka jádrová + štuk 2.NP; … (+13 dalších)</t>
         </is>
       </c>
       <c r="E144" s="20" t="inlineStr">
@@ -8942,8 +8942,88 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="20" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C145" s="21" t="inlineStr">
+        <is>
+          <t>PSV-95 — Detekce požární</t>
+        </is>
+      </c>
+      <c r="D145" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 3 položek: Autonomní hlásič kouře; Přenosný hasicí přístroj 34A; Předávací protokol krbu + kontrola bezpečných vzdáleností</t>
+        </is>
+      </c>
+      <c r="E145" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F145" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G145" s="10" t="n"/>
+      <c r="H145" s="10" t="n"/>
+      <c r="I145" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J145" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="20" t="inlineStr">
+        <is>
+          <t>260219_dum</t>
+        </is>
+      </c>
+      <c r="C146" s="21" t="inlineStr">
+        <is>
+          <t>VRN — Vedlejší rozpočtové náklady</t>
+        </is>
+      </c>
+      <c r="D146" s="8" t="inlineStr">
+        <is>
+          <t>[agregát] 18 položek: Buňky kancelář + sociální; Mobilní WC; El. odběr + vodovodní odběr stavby; … (+15 dalších)</t>
+        </is>
+      </c>
+      <c r="E146" s="20" t="inlineStr">
+        <is>
+          <t>kpl</t>
+        </is>
+      </c>
+      <c r="F146" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G146" s="10" t="n"/>
+      <c r="H146" s="10" t="n"/>
+      <c r="I146" s="8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J146" s="8" t="inlineStr">
+        <is>
+          <t>agregát</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J144"/>
+  <autoFilter ref="A1:J146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22785,7 +22865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R47"/>
+  <dimension ref="A1:R49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -23732,7 +23812,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Dvoustupňové patky pro IPE180 — horní část z tvarovek ztraceného bednění 300×300 mm × 6 ks</t>
+          <t>Patky parking horní část — zdivo z tvárnic ztraceného bednění 300×300 mm (lost formwork, zůstává v konstrukci), 6 patek á 300×300×500 mm</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -23776,7 +23856,7 @@
       <c r="P14" s="41" t="n"/>
       <c r="Q14" s="41" t="inlineStr">
         <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+          <t>TVARNICE_SPLIT_FIX_2026-06-02 — materiál-leg byl chybně ocel S235 (auto-split chytil IPE180); ztracené bednění → komplet</t>
         </is>
       </c>
     </row>
@@ -23810,7 +23890,7 @@
         </is>
       </c>
       <c r="G15" s="22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="H15" s="10" t="n"/>
       <c r="I15" s="10" t="n"/>
@@ -23829,7 +23909,7 @@
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec 2 řady nad 6 patkami, šířka tvárnic 300 mm</t>
+          <t>TZ statika sklad §3 + výkres D.1.1.02 — věnec délka 6.7 m (ruční obmer)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -23845,7 +23925,7 @@
       <c r="P15" s="41" t="n"/>
       <c r="Q15" s="41" t="inlineStr">
         <is>
-          <t>PATKY_7to6_DRAWING_2026-06-01</t>
+          <t>VENEC_6.7_2026-06-02</t>
         </is>
       </c>
     </row>
@@ -23997,41 +24077,41 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>H-BLOK opěrná stěna</t>
+          <t>Bednění základů (pasy + patky spodní)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>311233815</t>
+          <t>273351215</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
+          <t>Bednění základových pasů + spodních patek (prostý beton) — tradiční / systémové, oboustranné kde nelze betonovat do rýhy</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>18</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>25.4</v>
       </c>
       <c r="H18" s="10" t="n"/>
       <c r="I18" s="10" t="n"/>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>tesar</t>
         </is>
       </c>
       <c r="K18" s="24" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="L18" s="20" t="inlineStr">
         <is>
@@ -24040,12 +24120,12 @@
       </c>
       <c r="M18" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+          <t>výkres D.1.1.02 + řez — bednění základů; podíl do rýhy vs systémové OVĚŘIT</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#42</t>
         </is>
       </c>
       <c r="O18" s="26" t="inlineStr">
@@ -24053,16 +24133,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P18" s="41" t="inlineStr">
-        <is>
-          <t>S04_sklad</t>
-        </is>
-      </c>
-      <c r="Q18" s="41" t="inlineStr">
-        <is>
-          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P18" s="41" t="inlineStr"/>
+      <c r="Q18" s="41" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="20" t="n">
@@ -24070,41 +24142,41 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>HSV-3 Svislé konstrukce</t>
+          <t>HSV-2 Základové a ŽB</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Tvarovky ZB obvod skladu</t>
+          <t>Výztuž tvárnic ZB patek + věnce</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
         <is>
-          <t>311233811</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
+          <t>Výztuž B500B vkládaná do tvárnic ztraceného bednění — patky horní (6 sloupků) + ztužující věnec nad patkami</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G19" s="22" t="n">
-        <v>62.5</v>
+        <v>153</v>
       </c>
       <c r="H19" s="10" t="n"/>
       <c r="I19" s="10" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>zelezarsky</t>
         </is>
       </c>
       <c r="K19" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L19" s="20" t="inlineStr">
         <is>
@@ -24113,12 +24185,12 @@
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
+          <t>TZ statika sklad §3 — výztuž B500B do tvárnic ZB; sazba dle stěny S03a (HSV3.003)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#42</t>
         </is>
       </c>
       <c r="O19" s="26" t="inlineStr">
@@ -24126,16 +24198,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P19" s="41" t="inlineStr">
-        <is>
-          <t>S03a_sklad, S03b_sklad</t>
-        </is>
-      </c>
-      <c r="Q19" s="41" t="inlineStr">
-        <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P19" s="41" t="inlineStr"/>
+      <c r="Q19" s="41" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="20" t="n">
@@ -24148,49 +24212,50 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Výztuž ZB tvarovek</t>
+          <t>H-BLOK opěrná stěna</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>273361821</t>
+          <t>311233815</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
+          <t>Zadní opěrná stěna — prefabrikované betonové bloky Herkul H-BLOK Standard, vazba běhounová s posunem 0.5</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>1875</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>18</v>
       </c>
       <c r="H20" s="10" t="n"/>
       <c r="I20" s="10" t="n"/>
       <c r="J20" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K20" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L20" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M20" s="8">
-        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
-        <v/>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t>TZ statika sklad §[19] H-BLOK Standard Herkul + výkres D.1.1.02/D.1.1.03 — blok 1800×600 mm POTVRZENO výkresem (dříve web-analogie, nyní měřeno z výkresu); objem 6.35×3.0×0.6 = 11.43 m³</t>
+        </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
         <is>
-          <t>#8</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O20" s="26" t="inlineStr">
@@ -24200,12 +24265,12 @@
       </c>
       <c r="P20" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S03b_sklad</t>
+          <t>S04_sklad</t>
         </is>
       </c>
       <c r="Q20" s="41" t="inlineStr">
         <is>
-          <t>S03A_HEIGHT_3.5_2026-06-01</t>
+          <t>HBLOK_DRAWING_CONFIRMED_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24220,17 +24285,17 @@
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
+          <t>Tvarovky ZB obvod skladu</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>311233811</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
+          <t>Obvodové stěny skladu S03a/b — tvarovky ztraceného bednění tl. 250 mm, výška 14 řad × 250 = 3.5 m + zalití C25/30</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -24239,17 +24304,17 @@
         </is>
       </c>
       <c r="G21" s="22" t="n">
-        <v>33</v>
+        <v>62.5</v>
       </c>
       <c r="H21" s="10" t="n"/>
       <c r="I21" s="10" t="n"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K21" s="24" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="L21" s="20" t="inlineStr">
         <is>
@@ -24258,7 +24323,7 @@
       </c>
       <c r="M21" s="8" t="inlineStr">
         <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
+          <t>výkres D.1.1.02/03 — 14 řad tvárnic × 250 mm (řady začínají pod úrovní podlahy od pasu); světlá 2.68 je vnitřní svět, NE výška tvárnic</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -24273,12 +24338,12 @@
       </c>
       <c r="P21" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q21" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24293,50 +24358,49 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
+          <t>Výztuž ZB tvarovek</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>273361821</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
+          <t>Výztuž B500B do tvarovek ztraceného bednění (~30 kg/m² stěny při zalití C25/30)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G22" s="22" t="n">
-        <v>33</v>
+        <v>1875</v>
       </c>
       <c r="H22" s="10" t="n"/>
       <c r="I22" s="10" t="n"/>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K22" s="24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L22" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M22" s="8" t="inlineStr">
-        <is>
-          <t>skladba S03a+S04 řez D.1.1.03/04</t>
-        </is>
+          <t>family_verified_leaf_needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M22" s="8">
+        <f> HSV3.002 plocha (62.5 m²) × 30 kg/m²</f>
+        <v/>
       </c>
       <c r="N22" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#8</t>
         </is>
       </c>
       <c r="O22" s="26" t="inlineStr">
@@ -24346,12 +24410,12 @@
       </c>
       <c r="P22" s="41" t="inlineStr">
         <is>
-          <t>S03a_sklad, S04_sklad</t>
+          <t>S03a_sklad, S03b_sklad</t>
         </is>
       </c>
       <c r="Q22" s="41" t="inlineStr">
         <is>
-          <t>SKLAD_WALL_HI_2026-06-01</t>
+          <t>S03A_HEIGHT_3.5_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24361,41 +24425,41 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice skladu</t>
+          <t>Hydroizolace + protiradon stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
         <is>
-          <t>762341110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
+          <t>Hydroizolace + protiradonová ochrana obvodových stěn (S03a) + opěrné stěny (S04) pod úrovní terénu — asfaltová penetrace + 2× HI a protiradonový pás z modif. asfaltu 2×4 mm</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G23" s="22" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H23" s="10" t="n"/>
       <c r="I23" s="10" t="n"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K23" s="24" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L23" s="20" t="inlineStr">
         <is>
@@ -24404,7 +24468,7 @@
       </c>
       <c r="M23" s="8" t="inlineStr">
         <is>
-          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
+          <t>skladba S03a+S04 řez D.1.1.03/04 + legenda materiálu</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -24419,12 +24483,12 @@
       </c>
       <c r="P23" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q23" s="41" t="inlineStr">
         <is>
-          <t>TRAMY_10ks_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24434,22 +24498,22 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>HSV-4 Vodorovné</t>
+          <t>HSV-3 Svislé konstrukce</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropu skladu</t>
+          <t>Drenáž nopová folie stěn pod terénem (S03a+S04)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
         <is>
-          <t>762331110</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
+          <t>Drenážní vrstva — nopová folie tl. 20 mm na obvodové stěny (S03a) + opěrnou stěnu (S04) pod úrovní terénu</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -24458,26 +24522,27 @@
         </is>
       </c>
       <c r="G24" s="22" t="n">
-        <v>18.1</v>
+        <v>33</v>
       </c>
       <c r="H24" s="10" t="n"/>
       <c r="I24" s="10" t="n"/>
       <c r="J24" s="8" t="inlineStr">
         <is>
-          <t>krov_tesarsky_kompletni</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K24" s="24" t="n">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="L24" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M24" s="8">
-        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
-        <v/>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t>skladba S03a+S04 řez D.1.1.03/04</t>
+        </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
         <is>
@@ -24491,12 +24556,12 @@
       </c>
       <c r="P24" s="41" t="inlineStr">
         <is>
-          <t>S02_sklad</t>
+          <t>S03a_sklad, S04_sklad</t>
         </is>
       </c>
       <c r="Q24" s="41" t="inlineStr">
         <is>
-          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
+          <t>SKLAD_WALL_HI_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24511,32 +24576,32 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu</t>
+          <t>Dřevěné stropnice skladu</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
         <is>
-          <t>712331101</t>
+          <t>762341110</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
-          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
+          <t>Dřevěné stropnice 100/160 mm á 625 mm primární zastřešení skladu — rezivo C24 fungicidní</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G25" s="22" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H25" s="10" t="n"/>
       <c r="I25" s="10" t="n"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>izolater_HI</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K25" s="24" t="n">
@@ -24547,9 +24612,10 @@
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M25" s="8">
-        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
-        <v/>
+      <c r="M25" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 10× trám KVH 100/160; TZ rozpon 3.1 m</t>
+        </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
         <is>
@@ -24568,7 +24634,7 @@
       </c>
       <c r="Q25" s="41" t="inlineStr">
         <is>
-          <t>HI_TRAMY_BASE_2026-06-01</t>
+          <t>TRAMY_10ks_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24583,50 +24649,49 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>IPE180 parking — sekundární</t>
+          <t>Prkenný záklop stropu skladu</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
         <is>
-          <t>411321414</t>
+          <t>762331110</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
+          <t>Prkenný záklop stropnic skladu tl. 20 mm + impregnace</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G26" s="22" t="n">
-        <v>790</v>
+        <v>18.1</v>
       </c>
       <c r="H26" s="10" t="n"/>
       <c r="I26" s="10" t="n"/>
       <c r="J26" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>krov_tesarsky_kompletni</t>
         </is>
       </c>
       <c r="K26" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L26" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M26" s="8" t="inlineStr">
-        <is>
-          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
-        </is>
+      <c r="M26" s="8">
+        <f> plocha stropu nad trámy KVH (HSV4.001)</f>
+        <v/>
       </c>
       <c r="N26" s="20" t="inlineStr">
         <is>
-          <t>#18</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O26" s="26" t="inlineStr">
@@ -24641,7 +24706,7 @@
       </c>
       <c r="Q26" s="41" t="inlineStr">
         <is>
-          <t>IPE_7to6_DRAWING_2026-06-01</t>
+          <t>ZAKLOP_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24656,17 +24721,17 @@
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty</t>
+          <t>Hydroizolační střešní souvrství skladu</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
         <is>
-          <t>411321515</t>
+          <t>712331101</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
+          <t>Hydroizolační střešní souvrství skladu (modifikovaný asfaltový pás SBS + ochranná vrstva)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -24675,27 +24740,26 @@
         </is>
       </c>
       <c r="G27" s="22" t="n">
-        <v>44.6</v>
+        <v>19</v>
       </c>
       <c r="H27" s="10" t="n"/>
       <c r="I27" s="10" t="n"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>ocel_zamecnik_konstrukce</t>
+          <t>izolater_HI</t>
         </is>
       </c>
       <c r="K27" s="24" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="L27" s="20" t="inlineStr">
         <is>
-          <t>family_verified_leaf_needs_production_lookup</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
-        <is>
-          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
-        </is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M27" s="8">
+        <f> záklop (HSV4.002) × 1.05 přesah HI</f>
+        <v/>
       </c>
       <c r="N27" s="20" t="inlineStr">
         <is>
@@ -24714,7 +24778,7 @@
       </c>
       <c r="Q27" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
+          <t>HI_TRAMY_BASE_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24729,17 +24793,17 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Žárový zinek IPE + pororošty</t>
+          <t>IPE180 parking — sekundární</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
         <is>
-          <t>783201001</t>
+          <t>411321414</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
+          <t>Sekundární zastřešení parkingu — IPE180 v rozteči 1000 mm × délka 6 m × 6 ks</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -24748,7 +24812,7 @@
         </is>
       </c>
       <c r="G28" s="22" t="n">
-        <v>1420</v>
+        <v>790</v>
       </c>
       <c r="H28" s="10" t="n"/>
       <c r="I28" s="10" t="n"/>
@@ -24758,20 +24822,21 @@
         </is>
       </c>
       <c r="K28" s="24" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="L28" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M28" s="8">
-        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
-        <v/>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t>výkres D.1.1.02 — 6× IPE180 á 7.0 m; ČSN hmotnost 18.8 kg/m</t>
+        </is>
       </c>
       <c r="N28" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#18</t>
         </is>
       </c>
       <c r="O28" s="26" t="inlineStr">
@@ -24796,22 +24861,22 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + schodiště</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Schodiště prefa stupně</t>
+          <t>Pojezdové ocelové pororošty</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
         <is>
-          <t>121301101</t>
+          <t>411321515</t>
         </is>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
+          <t>Pojezdové ocelové pororošty demontovatelné — povrch parkingu (žárově zinkováno)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -24820,26 +24885,26 @@
         </is>
       </c>
       <c r="G29" s="22" t="n">
-        <v>5.5</v>
+        <v>44.6</v>
       </c>
       <c r="H29" s="10" t="n"/>
       <c r="I29" s="10" t="n"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>betonar</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K29" s="24" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L29" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>family_verified_leaf_needs_production_lookup</t>
         </is>
       </c>
       <c r="M29" s="8" t="inlineStr">
         <is>
-          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
+          <t>DXF sklad_DPZ km_tabulka místností + Phase 3.5 sklad qty crosscheck (Pattern 17 Phase 0a Layer 2 + Pattern 31 CEV Matrix D.2)</t>
         </is>
       </c>
       <c r="N29" s="20" t="inlineStr">
@@ -24854,12 +24919,12 @@
       </c>
       <c r="P29" s="41" t="inlineStr">
         <is>
-          <t>S05_sklad</t>
+          <t>S02_sklad</t>
         </is>
       </c>
       <c r="Q29" s="41" t="inlineStr">
         <is>
-          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+          <t>PHASE_3_5_SKLAD_QTY_DXF_VERIFY; URS_PHASE5B_FAMILY_VERIFIED</t>
         </is>
       </c>
     </row>
@@ -24869,51 +24934,50 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + vjezd</t>
+          <t>HSV-4 Vodorovné</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova — napojení na komunikaci</t>
+          <t>Žárový zinek IPE + pororošty</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>783201001</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
+          <t>Žárově zinková povrchová úprava IPE180 + pororoštů dle ČSN EN ISO 12944 (C3 prostředí)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="G30" s="22" t="n">
-        <v>7</v>
+        <v>1420</v>
       </c>
       <c r="H30" s="10" t="n"/>
       <c r="I30" s="10" t="n"/>
       <c r="J30" s="8" t="inlineStr">
         <is>
-          <t>komunikace</t>
+          <t>ocel_zamecnik_konstrukce</t>
         </is>
       </c>
       <c r="K30" s="24" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="L30" s="20" t="inlineStr">
         <is>
           <t>needs_production_lookup</t>
         </is>
       </c>
-      <c r="M30" s="8" t="inlineStr">
-        <is>
-          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
-        </is>
+      <c r="M30" s="8">
+        <f> HSV4.004 (6 ks) + HSV4.005 pororošt hmotnost</f>
+        <v/>
       </c>
       <c r="N30" s="20" t="inlineStr">
         <is>
@@ -24925,10 +24989,14 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P30" s="41" t="inlineStr"/>
+      <c r="P30" s="41" t="inlineStr">
+        <is>
+          <t>S02_sklad</t>
+        </is>
+      </c>
       <c r="Q30" s="41" t="inlineStr">
         <is>
-          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+          <t>IPE_7to6_DRAWING_2026-06-01</t>
         </is>
       </c>
     </row>
@@ -24938,41 +25006,41 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + zpevněné plochy</t>
+          <t>HSV-5 Komunikace + schodiště</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Vjezd — pískové lože</t>
+          <t>Schodiště prefa stupně</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
         <is>
-          <t>564751111</t>
+          <t>121301101</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
-          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
+          <t>Schodiště S05 — prefabrikované betonové stupně (2× 9 stupňů 179.5×250 + mezipodesta)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G31" s="22" t="n">
-        <v>0.28</v>
+        <v>5.5</v>
       </c>
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="10" t="n"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>betonar</t>
         </is>
       </c>
       <c r="K31" s="24" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="L31" s="20" t="inlineStr">
         <is>
@@ -24981,7 +25049,7 @@
       </c>
       <c r="M31" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+          <t>DXF sklad_DPZ km_tabulka místností room 1.02 + DXF dimension 9×179.5×250 mm + Phase 3.5 sklad S-code mapping (S05 sklad schodiště skladba)</t>
         </is>
       </c>
       <c r="N31" s="20" t="inlineStr">
@@ -24994,8 +25062,16 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P31" s="41" t="inlineStr"/>
-      <c r="Q31" s="41" t="n"/>
+      <c r="P31" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
+      <c r="Q31" s="41" t="inlineStr">
+        <is>
+          <t>PHASE_3_5_SKLAD_MEZIPODESTA_GAP</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="20" t="n">
@@ -25003,37 +25079,37 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>HSV-5 Komunikace + zpevněné plochy</t>
+          <t>HSV-5 Komunikace + vjezd</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Vjezd — štěrkový podklad</t>
+          <t>Vjezd Dvořákova — napojení na komunikaci</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
         <is>
-          <t>564861111</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
+          <t>Vjezd Dvořákova (POZN 01) — zpevněná plocha z hladké betonové dlažby, napojení na komunikaci</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G32" s="22" t="n">
-        <v>1.05</v>
+        <v>7</v>
       </c>
       <c r="H32" s="10" t="n"/>
       <c r="I32" s="10" t="n"/>
       <c r="J32" s="8" t="inlineStr">
         <is>
-          <t>zednik</t>
+          <t>komunikace</t>
         </is>
       </c>
       <c r="K32" s="24" t="n">
@@ -25046,7 +25122,7 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
+          <t>D.1.1.01 POZN 01 — zpevněná plocha betonová dlažba (= zóna napojení Dvořákova, nedupl.)</t>
         </is>
       </c>
       <c r="N32" s="20" t="inlineStr">
@@ -25060,7 +25136,11 @@
         </is>
       </c>
       <c r="P32" s="41" t="inlineStr"/>
-      <c r="Q32" s="41" t="n"/>
+      <c r="Q32" s="41" t="inlineStr">
+        <is>
+          <t>VJEZD_POZN01_7m2_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="20" t="n">
@@ -25073,26 +25153,26 @@
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Odvodňovací žlab</t>
+          <t>Vjezd — pískové lože</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>564751111</t>
         </is>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
+          <t>Pískové lože pod dlažbu vjezdu tl. 40 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G33" s="22" t="n">
-        <v>7.775</v>
+        <v>0.28</v>
       </c>
       <c r="H33" s="10" t="n"/>
       <c r="I33" s="10" t="n"/>
@@ -25111,7 +25191,7 @@
       </c>
       <c r="M33" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N33" s="20" t="inlineStr">
@@ -25138,17 +25218,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Odvodňovací žlab — podkladní beton</t>
+          <t>Vjezd — štěrkový podklad</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
         <is>
-          <t>273321411</t>
+          <t>564861111</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
+          <t>Štěrkový zhutněný podklad pod dlažbu vjezdu tl. 150 mm (POZN 01)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -25157,7 +25237,7 @@
         </is>
       </c>
       <c r="G34" s="22" t="n">
-        <v>0.47</v>
+        <v>1.05</v>
       </c>
       <c r="H34" s="10" t="n"/>
       <c r="I34" s="10" t="n"/>
@@ -25176,7 +25256,7 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
+          <t>D.1.1.01 POZN 01 — souvrství pod dlažbu</t>
         </is>
       </c>
       <c r="N34" s="20" t="inlineStr">
@@ -25203,7 +25283,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Okapový žlab</t>
+          <t>Odvodňovací žlab</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -25213,7 +25293,7 @@
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
+          <t>Liniový odvodňovací žlab (prefa žlabovka š. 160 mm) podél vjezdu</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -25222,7 +25302,7 @@
         </is>
       </c>
       <c r="G35" s="22" t="n">
-        <v>6</v>
+        <v>7.775</v>
       </c>
       <c r="H35" s="10" t="n"/>
       <c r="I35" s="10" t="n"/>
@@ -25232,7 +25312,7 @@
         </is>
       </c>
       <c r="K35" s="24" t="n">
-        <v>0.65</v>
+        <v>0.75</v>
       </c>
       <c r="L35" s="20" t="inlineStr">
         <is>
@@ -25241,7 +25321,7 @@
       </c>
       <c r="M35" s="8" t="inlineStr">
         <is>
-          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
+          <t>D.1.1.01 + detail — žlabovka 160 mm na podkl. betonu (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="N35" s="20" t="inlineStr">
@@ -25268,36 +25348,36 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Schodiště — podkladní deska</t>
+          <t>Odvodňovací žlab — podkladní beton</t>
         </is>
       </c>
       <c r="D36" s="20" t="inlineStr">
         <is>
-          <t>273313611</t>
+          <t>273321411</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>Podkladní betonová deska pod prefa schodiště S05</t>
+          <t>Podkladní beton pod odvodňovací žlab (průřez 0.06 m²)</t>
         </is>
       </c>
       <c r="F36" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G36" s="22" t="n">
-        <v>5.5</v>
+        <v>0.47</v>
       </c>
       <c r="H36" s="10" t="n"/>
       <c r="I36" s="10" t="n"/>
       <c r="J36" s="8" t="inlineStr">
         <is>
-          <t>zelezobetonarsky_specialny</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K36" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L36" s="20" t="inlineStr">
         <is>
@@ -25306,12 +25386,12 @@
       </c>
       <c r="M36" s="8" t="inlineStr">
         <is>
-          <t>skladba S05 — podkladní betonová deska</t>
+          <t>detail řezu žlabu — průřez betonového lože 0.06 m²</t>
         </is>
       </c>
       <c r="N36" s="20" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O36" s="26" t="inlineStr">
@@ -25319,11 +25399,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P36" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="P36" s="41" t="inlineStr"/>
       <c r="Q36" s="41" t="n"/>
     </row>
     <row r="37">
@@ -25337,7 +25413,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Schodiště — kladecí beton</t>
+          <t>Okapový žlab</t>
         </is>
       </c>
       <c r="D37" s="20" t="inlineStr">
@@ -25347,16 +25423,16 @@
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
+          <t>Okapový/odvodňovací žlab na straně 6010 mm — typ OVĚŘIT</t>
         </is>
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G37" s="22" t="n">
-        <v>0.28</v>
+        <v>6</v>
       </c>
       <c r="H37" s="10" t="n"/>
       <c r="I37" s="10" t="n"/>
@@ -25366,7 +25442,7 @@
         </is>
       </c>
       <c r="K37" s="24" t="n">
-        <v>0.7</v>
+        <v>0.65</v>
       </c>
       <c r="L37" s="20" t="inlineStr">
         <is>
@@ -25375,12 +25451,12 @@
       </c>
       <c r="M37" s="8" t="inlineStr">
         <is>
-          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
+          <t>řez — žlab na straně 6010; typ (okapový/liniový) OVĚŘIT</t>
         </is>
       </c>
       <c r="N37" s="20" t="inlineStr">
         <is>
-          <t>#41</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O37" s="26" t="inlineStr">
@@ -25388,11 +25464,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P37" s="41" t="inlineStr">
-        <is>
-          <t>S05_sklad</t>
-        </is>
-      </c>
+      <c r="P37" s="41" t="inlineStr"/>
       <c r="Q37" s="41" t="n"/>
     </row>
     <row r="38">
@@ -25401,41 +25473,41 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Výplně otvorů</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 sklad</t>
+          <t>Schodiště — podkladní deska</t>
         </is>
       </c>
       <c r="D38" s="20" t="inlineStr">
         <is>
-          <t>766682111</t>
+          <t>273313611</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
+          <t>Podkladní betonová deska pod prefa schodiště S05</t>
         </is>
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G38" s="23" t="n">
-        <v>1</v>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="G38" s="22" t="n">
+        <v>5.5</v>
       </c>
       <c r="H38" s="10" t="n"/>
       <c r="I38" s="10" t="n"/>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t>specialista_RC3_dvere</t>
+          <t>zelezobetonarsky_specialny</t>
         </is>
       </c>
       <c r="K38" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L38" s="20" t="inlineStr">
         <is>
@@ -25444,12 +25516,12 @@
       </c>
       <c r="M38" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
+          <t>skladba S05 — podkladní betonová deska</t>
         </is>
       </c>
       <c r="N38" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O38" s="26" t="inlineStr">
@@ -25457,7 +25529,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P38" s="41" t="n"/>
+      <c r="P38" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q38" s="41" t="n"/>
     </row>
     <row r="39">
@@ -25466,12 +25542,12 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>HSV-5 Komunikace + zpevněné plochy</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Oplocení (plot)</t>
+          <t>Schodiště — kladecí beton</t>
         </is>
       </c>
       <c r="D39" s="20" t="inlineStr">
@@ -25481,22 +25557,22 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Kladecí vrstva ze zavlhlého betonu pod prefa stupně S05</t>
         </is>
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="G39" s="22" t="n">
-        <v>3.8</v>
+        <v>0.28</v>
       </c>
       <c r="H39" s="10" t="n"/>
       <c r="I39" s="10" t="n"/>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>zednik</t>
         </is>
       </c>
       <c r="K39" s="24" t="n">
@@ -25509,12 +25585,12 @@
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
+          <t>skladba S05 — kladecí vrstva zavlhlý beton</t>
         </is>
       </c>
       <c r="N39" s="20" t="inlineStr">
         <is>
-          <t>#37</t>
+          <t>#41</t>
         </is>
       </c>
       <c r="O39" s="26" t="inlineStr">
@@ -25522,7 +25598,11 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P39" s="41" t="inlineStr"/>
+      <c r="P39" s="41" t="inlineStr">
+        <is>
+          <t>S05_sklad</t>
+        </is>
+      </c>
       <c r="Q39" s="41" t="n"/>
     </row>
     <row r="40">
@@ -25531,41 +25611,41 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnické konstrukce</t>
+          <t>PSV-76 Výplně otvorů</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí stání</t>
+          <t>Bezpečnostní dveře RC3 sklad</t>
         </is>
       </c>
       <c r="D40" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>766682111</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
+          <t>Bezpečnostní dveře RC3 v ocelové zárubni — vrata skladu (TZ statika §1.4 RC3 certifikované)</t>
         </is>
       </c>
       <c r="F40" s="20" t="inlineStr">
         <is>
-          <t>bm</t>
-        </is>
-      </c>
-      <c r="G40" s="22" t="n">
-        <v>18.5</v>
+          <t>ks</t>
+        </is>
+      </c>
+      <c r="G40" s="23" t="n">
+        <v>1</v>
       </c>
       <c r="H40" s="10" t="n"/>
       <c r="I40" s="10" t="n"/>
       <c r="J40" s="8" t="inlineStr">
         <is>
-          <t>zamecnik</t>
+          <t>specialista_RC3_dvere</t>
         </is>
       </c>
       <c r="K40" s="24" t="n">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="L40" s="20" t="inlineStr">
         <is>
@@ -25574,12 +25654,12 @@
       </c>
       <c r="M40" s="8" t="inlineStr">
         <is>
-          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
+          <t>TZ statika sklad §1.4 — RC3 bezpečnostní dveře v ocelové zárubni</t>
         </is>
       </c>
       <c r="N40" s="20" t="inlineStr">
         <is>
-          <t>#38</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O40" s="26" t="inlineStr">
@@ -25587,7 +25667,7 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P40" s="41" t="inlineStr"/>
+      <c r="P40" s="41" t="n"/>
       <c r="Q40" s="41" t="n"/>
     </row>
     <row r="41">
@@ -25596,12 +25676,12 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>PSV-76 Zámečnictví</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána</t>
+          <t>Oplocení (plot)</t>
         </is>
       </c>
       <c r="D41" s="20" t="inlineStr">
@@ -25611,16 +25691,16 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
+          <t>Oplocení podél vjezdu — délka dle situace, materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F41" s="20" t="inlineStr">
         <is>
-          <t>ks</t>
-        </is>
-      </c>
-      <c r="G41" s="23" t="n">
-        <v>1</v>
+          <t>bm</t>
+        </is>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>3.8</v>
       </c>
       <c r="H41" s="10" t="n"/>
       <c r="I41" s="10" t="n"/>
@@ -25630,7 +25710,7 @@
         </is>
       </c>
       <c r="K41" s="24" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="L41" s="20" t="inlineStr">
         <is>
@@ -25639,12 +25719,12 @@
       </c>
       <c r="M41" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01)</t>
+          <t>D.1.1.01 půdorys střechy — plot u vjezdu; materiál + přesná délka OVĚŘIT</t>
         </is>
       </c>
       <c r="N41" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#37</t>
         </is>
       </c>
       <c r="O41" s="26" t="inlineStr">
@@ -25653,11 +25733,7 @@
         </is>
       </c>
       <c r="P41" s="41" t="inlineStr"/>
-      <c r="Q41" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="Q41" s="41" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="20" t="n">
@@ -25665,72 +25741,64 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>PSV-77 Podlahy</t>
+          <t>PSV-76 Zámečnické konstrukce</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba sklad</t>
-        </is>
-      </c>
-      <c r="D42" s="27" t="inlineStr">
-        <is>
-          <t>596??? ?</t>
+          <t>Zábradlí stání</t>
+        </is>
+      </c>
+      <c r="D42" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
+          <t>Zábradlí v. 1.0 m kolem části stání — materiál OVĚŘIT (kov/dřevo neuveden)</t>
         </is>
       </c>
       <c r="F42" s="20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bm</t>
         </is>
       </c>
       <c r="G42" s="22" t="n">
-        <v>23.6</v>
+        <v>18.5</v>
       </c>
       <c r="H42" s="10" t="n"/>
       <c r="I42" s="10" t="n"/>
       <c r="J42" s="8" t="inlineStr">
         <is>
-          <t>podlahar</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K42" s="24" t="n">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="L42" s="20" t="inlineStr">
         <is>
-          <t>wrong_leaf_disambiguation_needed</t>
+          <t>needs_production_lookup</t>
         </is>
       </c>
       <c r="M42" s="8" t="inlineStr">
         <is>
-          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
+          <t>D.1.1.01 — zábradlí 1.0 m kolem části plochy; materiál OVĚŘIT</t>
         </is>
       </c>
       <c r="N42" s="20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O42" s="28" t="inlineStr">
-        <is>
-          <t>LEAF CHYBNÝ — viz alternatives</t>
-        </is>
-      </c>
-      <c r="P42" s="41" t="inlineStr">
-        <is>
-          <t>S01_sklad</t>
-        </is>
-      </c>
-      <c r="Q42" s="41" t="inlineStr">
-        <is>
-          <t>S01_AREA_23.6_2026-06-01</t>
-        </is>
-      </c>
+          <t>#38</t>
+        </is>
+      </c>
+      <c r="O42" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P42" s="41" t="inlineStr"/>
+      <c r="Q42" s="41" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="20" t="n">
@@ -25738,27 +25806,27 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-76 Zámečnictví</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
+          <t>Vjezdová brána</t>
         </is>
       </c>
       <c r="D43" s="20" t="inlineStr">
         <is>
-          <t>031032000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
+          <t>Vjezdová brána na pozemku investora (ocelová) — dodávka + montáž</t>
         </is>
       </c>
       <c r="F43" s="20" t="inlineStr">
         <is>
-          <t>kpl</t>
+          <t>ks</t>
         </is>
       </c>
       <c r="G43" s="23" t="n">
@@ -25768,11 +25836,11 @@
       <c r="I43" s="10" t="n"/>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>prefa_bloky_specialista</t>
+          <t>zamecnik</t>
         </is>
       </c>
       <c r="K43" s="24" t="n">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="L43" s="20" t="inlineStr">
         <is>
@@ -25781,7 +25849,7 @@
       </c>
       <c r="M43" s="8" t="inlineStr">
         <is>
-          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
+          <t>Dodatek PD č.1 (E.01)</t>
         </is>
       </c>
       <c r="N43" s="20" t="inlineStr">
@@ -25794,8 +25862,12 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P43" s="41" t="n"/>
-      <c r="Q43" s="41" t="n"/>
+      <c r="P43" s="41" t="inlineStr"/>
+      <c r="Q43" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="20" t="n">
@@ -25803,50 +25875,50 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>VRN — Doprava + odpad</t>
+          <t>PSV-77 Podlahy</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad</t>
-        </is>
-      </c>
-      <c r="D44" s="20" t="inlineStr">
-        <is>
-          <t>997013211</t>
+          <t>Betonová dlažba sklad</t>
+        </is>
+      </c>
+      <c r="D44" s="27" t="inlineStr">
+        <is>
+          <t>596??? ?</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
+          <t>Betonová dlažba 50 mm do kladecího lože — podlaha skladu + vynos za stěnu</t>
         </is>
       </c>
       <c r="F44" s="20" t="inlineStr">
         <is>
-          <t>t</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="G44" s="22" t="n">
-        <v>8</v>
+        <v>23.6</v>
       </c>
       <c r="H44" s="10" t="n"/>
       <c r="I44" s="10" t="n"/>
       <c r="J44" s="8" t="inlineStr">
         <is>
-          <t>bourani_demolice</t>
+          <t>podlahar</t>
         </is>
       </c>
       <c r="K44" s="24" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="L44" s="20" t="inlineStr">
         <is>
-          <t>needs_production_lookup</t>
+          <t>wrong_leaf_disambiguation_needed</t>
         </is>
       </c>
       <c r="M44" s="8" t="inlineStr">
         <is>
-          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
+          <t>legenda místností 17.6 + vynos S01 za stěnu (řez B-B)</t>
         </is>
       </c>
       <c r="N44" s="20" t="inlineStr">
@@ -25854,13 +25926,21 @@
           <t>—</t>
         </is>
       </c>
-      <c r="O44" s="26" t="inlineStr">
-        <is>
-          <t>ANO</t>
-        </is>
-      </c>
-      <c r="P44" s="41" t="n"/>
-      <c r="Q44" s="41" t="n"/>
+      <c r="O44" s="28" t="inlineStr">
+        <is>
+          <t>LEAF CHYBNÝ — viz alternatives</t>
+        </is>
+      </c>
+      <c r="P44" s="41" t="inlineStr">
+        <is>
+          <t>S01_sklad</t>
+        </is>
+      </c>
+      <c r="Q44" s="41" t="inlineStr">
+        <is>
+          <t>S01_AREA_23.6_2026-06-01</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="20" t="n">
@@ -25868,22 +25948,22 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad</t>
+          <t>Doprava prefa H-BLOK auto s hyd. rukou</t>
         </is>
       </c>
       <c r="D45" s="20" t="inlineStr">
         <is>
-          <t>030141000</t>
+          <t>031032000</t>
         </is>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
+          <t>Doprava prefa H-BLOK Standard z výrobny Herkul (Obrnice) auto s hydraulickou rukou — celkem ~60 ks bloků</t>
         </is>
       </c>
       <c r="F45" s="20" t="inlineStr">
@@ -25898,11 +25978,11 @@
       <c r="I45" s="10" t="n"/>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>prefa_bloky_specialista</t>
         </is>
       </c>
       <c r="K45" s="24" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="L45" s="20" t="inlineStr">
         <is>
@@ -25911,7 +25991,7 @@
       </c>
       <c r="M45" s="8" t="inlineStr">
         <is>
-          <t>Standard — geodet vytýčení pro každý nový objekt</t>
+          <t>TZ statika sklad §4 + ARS — auto s hyd. rukou pro osazení H-BLOK</t>
         </is>
       </c>
       <c r="N45" s="20" t="inlineStr">
@@ -25933,41 +26013,41 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>VRN — Geodet / PČR</t>
+          <t>VRN — Doprava + odpad</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+          <t>Likvidace odpadu sklad</t>
         </is>
       </c>
       <c r="D46" s="20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>997013211</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+          <t>Likvidace odpadu sklad — kameny ze zídek + výkop + dřevo (drobné množství)</t>
         </is>
       </c>
       <c r="F46" s="20" t="inlineStr">
         <is>
-          <t>soubor</t>
-        </is>
-      </c>
-      <c r="G46" s="23" t="n">
-        <v>1</v>
+          <t>t</t>
+        </is>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>8</v>
       </c>
       <c r="H46" s="10" t="n"/>
       <c r="I46" s="10" t="n"/>
       <c r="J46" s="8" t="inlineStr">
         <is>
-          <t>geodet</t>
+          <t>bourani_demolice</t>
         </is>
       </c>
       <c r="K46" s="24" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="L46" s="20" t="inlineStr">
         <is>
@@ -25976,7 +26056,7 @@
       </c>
       <c r="M46" s="8" t="inlineStr">
         <is>
-          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+          <t>TZ ARS sklad §3 — kamenné zídky + schodiště odstraneny</t>
         </is>
       </c>
       <c r="N46" s="20" t="inlineStr">
@@ -25989,12 +26069,8 @@
           <t>ANO</t>
         </is>
       </c>
-      <c r="P46" s="41" t="inlineStr"/>
-      <c r="Q46" s="41" t="inlineStr">
-        <is>
-          <t>DODATEK_PBR_GAPS_2026-06-01</t>
-        </is>
-      </c>
+      <c r="P46" s="41" t="n"/>
+      <c r="Q46" s="41" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="20" t="n">
@@ -26002,27 +26078,27 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>VRN — Společné</t>
+          <t>VRN — Geodet</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN dům</t>
+          <t>Geodetické vytýčení sklad</t>
         </is>
       </c>
       <c r="D47" s="20" t="inlineStr">
         <is>
-          <t>030001000</t>
+          <t>030141000</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+          <t>Geodetické vytýčení sklad+parking+schodiště ze situace (před realizací)</t>
         </is>
       </c>
       <c r="F47" s="20" t="inlineStr">
         <is>
-          <t>paušál</t>
+          <t>kpl</t>
         </is>
       </c>
       <c r="G47" s="23" t="n">
@@ -26032,11 +26108,11 @@
       <c r="I47" s="10" t="n"/>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>VRN_management</t>
+          <t>geodet</t>
         </is>
       </c>
       <c r="K47" s="24" t="n">
-        <v>0.8</v>
+        <v>0.99</v>
       </c>
       <c r="L47" s="20" t="inlineStr">
         <is>
@@ -26045,7 +26121,7 @@
       </c>
       <c r="M47" s="8" t="inlineStr">
         <is>
-          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+          <t>Standard — geodet vytýčení pro každý nový objekt</t>
         </is>
       </c>
       <c r="N47" s="20" t="inlineStr">
@@ -26061,9 +26137,143 @@
       <c r="P47" s="41" t="n"/>
       <c r="Q47" s="41" t="n"/>
     </row>
+    <row r="48">
+      <c r="A48" s="20" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Geodet / PČR</t>
+        </is>
+      </c>
+      <c r="C48" s="8" t="inlineStr">
+        <is>
+          <t>Rozhledové trojúhelníky — vytyčení + kontrola</t>
+        </is>
+      </c>
+      <c r="D48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr">
+        <is>
+          <t>Vytyčení + kontrola rozhledových trojúhelníků (Vn=40 km/h, Dz=25 m) dle požadavku DI PČR</t>
+        </is>
+      </c>
+      <c r="F48" s="20" t="inlineStr">
+        <is>
+          <t>soubor</t>
+        </is>
+      </c>
+      <c r="G48" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="10" t="n"/>
+      <c r="I48" s="10" t="n"/>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>geodet</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L48" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M48" s="8" t="inlineStr">
+        <is>
+          <t>Dodatek PD č.1 (E.01) / DI PČR</t>
+        </is>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O48" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P48" s="41" t="inlineStr"/>
+      <c r="Q48" s="41" t="inlineStr">
+        <is>
+          <t>DODATEK_PBR_GAPS_2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="8" t="inlineStr">
+        <is>
+          <t>VRN — Společné</t>
+        </is>
+      </c>
+      <c r="C49" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN dům</t>
+        </is>
+      </c>
+      <c r="D49" s="20" t="inlineStr">
+        <is>
+          <t>030001000</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="inlineStr">
+        <is>
+          <t>Podíl na obecných VRN domu (buňky, BOZP, pojištění, kolaudace) — paušál ~10 % nákladů sklad nebo % alokace</t>
+        </is>
+      </c>
+      <c r="F49" s="20" t="inlineStr">
+        <is>
+          <t>paušál</t>
+        </is>
+      </c>
+      <c r="G49" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="10" t="n"/>
+      <c r="I49" s="10" t="n"/>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>VRN_management</t>
+        </is>
+      </c>
+      <c r="K49" s="24" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>needs_production_lookup</t>
+        </is>
+      </c>
+      <c r="M49" s="8" t="inlineStr">
+        <is>
+          <t>Standard zhotovitel — alokace VRN pro paralelně realizovaný sklad</t>
+        </is>
+      </c>
+      <c r="N49" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O49" s="26" t="inlineStr">
+        <is>
+          <t>ANO</t>
+        </is>
+      </c>
+      <c r="P49" s="41" t="n"/>
+      <c r="Q49" s="41" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O47"/>
-  <conditionalFormatting sqref="K2:K47">
+  <autoFilter ref="A1:O49"/>
+  <conditionalFormatting sqref="K2:K49">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0" stopIfTrue="1">
       <formula>0.70</formula>
     </cfRule>
